--- a/artfynd/A 14019-2025 artfynd.xlsx
+++ b/artfynd/A 14019-2025 artfynd.xlsx
@@ -1093,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123651434</v>
+        <v>123648670</v>
       </c>
       <c r="B6" t="n">
-        <v>98379</v>
+        <v>92247</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1105,41 +1105,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Tinnsjön, Tinnsjön, Sm</t>
+          <t>Hultsfred, Hultsfred, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>540454</v>
+        <v>540535</v>
       </c>
       <c r="R6" t="n">
-        <v>6348489</v>
+        <v>6348224</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1195,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123648670</v>
+        <v>123651434</v>
       </c>
       <c r="B7" t="n">
-        <v>92247</v>
+        <v>98379</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1207,41 +1207,41 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Hultsfred, Hultsfred, Sm</t>
+          <t>Tinnsjön, Tinnsjön, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>540535</v>
+        <v>540454</v>
       </c>
       <c r="R7" t="n">
-        <v>6348224</v>
+        <v>6348489</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -3245,10 +3245,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123677388</v>
+        <v>123678423</v>
       </c>
       <c r="B27" t="n">
-        <v>57634</v>
+        <v>100645</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3257,46 +3257,41 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103021</v>
+        <v>222498</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Tinnsjön, Tinnsjön, Sm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>540515</v>
+        <v>540463</v>
       </c>
       <c r="R27" t="n">
-        <v>6348462</v>
+        <v>6348528</v>
       </c>
       <c r="S27" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3352,10 +3347,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123678423</v>
+        <v>123677388</v>
       </c>
       <c r="B28" t="n">
-        <v>100645</v>
+        <v>57634</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3364,41 +3359,46 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>222498</v>
+        <v>103021</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Tinnsjön, Tinnsjön, Sm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>540463</v>
+        <v>540515</v>
       </c>
       <c r="R28" t="n">
-        <v>6348528</v>
+        <v>6348462</v>
       </c>
       <c r="S28" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>

--- a/artfynd/A 14019-2025 artfynd.xlsx
+++ b/artfynd/A 14019-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123655187</v>
+        <v>123648565</v>
       </c>
       <c r="B2" t="n">
-        <v>92247</v>
+        <v>91003</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,41 +687,41 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Tinnsjön, Tinnsjön, Sm</t>
+          <t>Hultsfred, Hultsfred, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>540525</v>
+        <v>540519</v>
       </c>
       <c r="R2" t="n">
-        <v>6348308</v>
+        <v>6348230</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123651343</v>
+        <v>123652358</v>
       </c>
       <c r="B3" t="n">
-        <v>100645</v>
+        <v>57503</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>540457</v>
+        <v>540555</v>
       </c>
       <c r="R3" t="n">
-        <v>6348499</v>
+        <v>6348531</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -853,6 +853,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-31</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123649033</v>
+        <v>123651753</v>
       </c>
       <c r="B4" t="n">
-        <v>57497</v>
+        <v>57857</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,20 +896,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -913,19 +918,24 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Tinnsjön, Tinnsjön, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>540498</v>
+        <v>540454</v>
       </c>
       <c r="R4" t="n">
-        <v>6348264</v>
+        <v>6348509</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -955,11 +965,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-31</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -986,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123651753</v>
+        <v>123654838</v>
       </c>
       <c r="B5" t="n">
-        <v>57851</v>
+        <v>98396</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -998,46 +1003,41 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Tinnsjön, Tinnsjön, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>540454</v>
+        <v>540648</v>
       </c>
       <c r="R5" t="n">
-        <v>6348509</v>
+        <v>6348392</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1093,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123648670</v>
+        <v>123655187</v>
       </c>
       <c r="B6" t="n">
-        <v>92247</v>
+        <v>92264</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1129,14 +1129,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hultsfred, Hultsfred, Sm</t>
+          <t>Tinnsjön, Tinnsjön, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>540535</v>
+        <v>540525</v>
       </c>
       <c r="R6" t="n">
-        <v>6348224</v>
+        <v>6348308</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1195,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123651434</v>
+        <v>123651343</v>
       </c>
       <c r="B7" t="n">
-        <v>98379</v>
+        <v>100662</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1207,25 +1207,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1235,13 +1235,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>540454</v>
+        <v>540457</v>
       </c>
       <c r="R7" t="n">
-        <v>6348489</v>
+        <v>6348499</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1297,10 +1297,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123650824</v>
+        <v>123654517</v>
       </c>
       <c r="B8" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1337,13 +1337,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>540485</v>
+        <v>540625</v>
       </c>
       <c r="R8" t="n">
-        <v>6348449</v>
+        <v>6348461</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1399,10 +1399,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123651626</v>
+        <v>123651434</v>
       </c>
       <c r="B9" t="n">
-        <v>100645</v>
+        <v>98396</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1411,25 +1411,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1439,13 +1439,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>540438</v>
+        <v>540454</v>
       </c>
       <c r="R9" t="n">
-        <v>6348476</v>
+        <v>6348489</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1501,10 +1501,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123654095</v>
+        <v>123649033</v>
       </c>
       <c r="B10" t="n">
-        <v>98379</v>
+        <v>57503</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1513,25 +1513,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1541,13 +1541,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>540624</v>
+        <v>540498</v>
       </c>
       <c r="R10" t="n">
-        <v>6348499</v>
+        <v>6348264</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1577,6 +1577,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-03-31</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1603,10 +1608,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123654838</v>
+        <v>123651999</v>
       </c>
       <c r="B11" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1643,13 +1648,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>540648</v>
+        <v>540507</v>
       </c>
       <c r="R11" t="n">
-        <v>6348392</v>
+        <v>6348554</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1705,10 +1710,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123651593</v>
+        <v>123651626</v>
       </c>
       <c r="B12" t="n">
-        <v>98379</v>
+        <v>100662</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1717,25 +1722,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1745,10 +1750,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>540446</v>
+        <v>540438</v>
       </c>
       <c r="R12" t="n">
-        <v>6348497</v>
+        <v>6348476</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1807,10 +1812,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123648565</v>
+        <v>123651201</v>
       </c>
       <c r="B13" t="n">
-        <v>90986</v>
+        <v>98396</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1819,41 +1824,41 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Hultsfred, Hultsfred, Sm</t>
+          <t>Tinnsjön, Tinnsjön, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>540519</v>
+        <v>540472</v>
       </c>
       <c r="R13" t="n">
-        <v>6348230</v>
+        <v>6348468</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1909,10 +1914,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123651201</v>
+        <v>123651287</v>
       </c>
       <c r="B14" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1949,13 +1954,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>540472</v>
+        <v>540463</v>
       </c>
       <c r="R14" t="n">
-        <v>6348468</v>
+        <v>6348492</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2011,10 +2016,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123651287</v>
+        <v>123653838</v>
       </c>
       <c r="B15" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2051,10 +2056,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>540463</v>
+        <v>540614</v>
       </c>
       <c r="R15" t="n">
-        <v>6348492</v>
+        <v>6348556</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2113,10 +2118,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123648212</v>
+        <v>123654095</v>
       </c>
       <c r="B16" t="n">
-        <v>94996</v>
+        <v>98396</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2125,38 +2130,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>210</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Hultsfred, Hultsfred, Sm</t>
+          <t>Tinnsjön, Tinnsjön, Sm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>540478</v>
+        <v>540624</v>
       </c>
       <c r="R16" t="n">
-        <v>6348196</v>
+        <v>6348499</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2215,10 +2220,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123652072</v>
+        <v>123650824</v>
       </c>
       <c r="B17" t="n">
-        <v>5173</v>
+        <v>98396</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2227,25 +2232,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2255,13 +2260,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>540512</v>
+        <v>540485</v>
       </c>
       <c r="R17" t="n">
-        <v>6348547</v>
+        <v>6348449</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2291,11 +2296,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-03-31</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2322,10 +2322,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123652358</v>
+        <v>123648212</v>
       </c>
       <c r="B18" t="n">
-        <v>57497</v>
+        <v>95013</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2334,41 +2334,41 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>210</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Tinnsjön, Tinnsjön, Sm</t>
+          <t>Hultsfred, Hultsfred, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>540555</v>
+        <v>540478</v>
       </c>
       <c r="R18" t="n">
-        <v>6348531</v>
+        <v>6348196</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2398,11 +2398,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-03-31</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2429,10 +2424,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123651999</v>
+        <v>123651593</v>
       </c>
       <c r="B19" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2469,13 +2464,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>540507</v>
+        <v>540446</v>
       </c>
       <c r="R19" t="n">
-        <v>6348554</v>
+        <v>6348497</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2531,10 +2526,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123654517</v>
+        <v>123648670</v>
       </c>
       <c r="B20" t="n">
-        <v>98379</v>
+        <v>92264</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2543,41 +2538,41 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Tinnsjön, Tinnsjön, Sm</t>
+          <t>Hultsfred, Hultsfred, Sm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>540625</v>
+        <v>540535</v>
       </c>
       <c r="R20" t="n">
-        <v>6348461</v>
+        <v>6348224</v>
       </c>
       <c r="S20" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2636,7 +2631,7 @@
         <v>123653223</v>
       </c>
       <c r="B21" t="n">
-        <v>95967</v>
+        <v>95984</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2735,10 +2730,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123653838</v>
+        <v>123652072</v>
       </c>
       <c r="B22" t="n">
-        <v>98379</v>
+        <v>5174</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2747,25 +2742,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2775,10 +2770,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>540614</v>
+        <v>540512</v>
       </c>
       <c r="R22" t="n">
-        <v>6348556</v>
+        <v>6348547</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2811,6 +2806,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-03-31</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2837,10 +2837,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123676068</v>
+        <v>123678423</v>
       </c>
       <c r="B23" t="n">
-        <v>97333</v>
+        <v>100662</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2853,37 +2853,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221945</v>
+        <v>222498</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Hultsfred, Hultsfred, Sm</t>
+          <t>Tinnsjön, Tinnsjön, Sm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>540573</v>
+        <v>540463</v>
       </c>
       <c r="R23" t="n">
-        <v>6348225</v>
+        <v>6348528</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2939,10 +2939,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123676891</v>
+        <v>123677321</v>
       </c>
       <c r="B24" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2979,10 +2979,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>540557</v>
+        <v>540504</v>
       </c>
       <c r="R24" t="n">
-        <v>6348447</v>
+        <v>6348434</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3044,7 +3044,7 @@
         <v>123677186</v>
       </c>
       <c r="B25" t="n">
-        <v>92247</v>
+        <v>92264</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3143,10 +3143,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123677321</v>
+        <v>123676891</v>
       </c>
       <c r="B26" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3183,10 +3183,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>540504</v>
+        <v>540557</v>
       </c>
       <c r="R26" t="n">
-        <v>6348434</v>
+        <v>6348447</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3245,10 +3245,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123678423</v>
+        <v>123677388</v>
       </c>
       <c r="B27" t="n">
-        <v>100645</v>
+        <v>57640</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3257,41 +3257,46 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>222498</v>
+        <v>103021</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Tinnsjön, Tinnsjön, Sm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>540463</v>
+        <v>540515</v>
       </c>
       <c r="R27" t="n">
-        <v>6348528</v>
+        <v>6348462</v>
       </c>
       <c r="S27" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3347,10 +3352,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123677388</v>
+        <v>123676068</v>
       </c>
       <c r="B28" t="n">
-        <v>57634</v>
+        <v>97350</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3359,46 +3364,41 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103021</v>
+        <v>221945</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Tinnsjön, Tinnsjön, Sm</t>
+          <t>Hultsfred, Hultsfred, Sm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>540515</v>
+        <v>540573</v>
       </c>
       <c r="R28" t="n">
-        <v>6348462</v>
+        <v>6348225</v>
       </c>
       <c r="S28" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>

--- a/artfynd/A 14019-2025 artfynd.xlsx
+++ b/artfynd/A 14019-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY28"/>
+  <dimension ref="A1:AY32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2526,10 +2526,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123648670</v>
+        <v>123653223</v>
       </c>
       <c r="B20" t="n">
-        <v>92264</v>
+        <v>95984</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2542,37 +2542,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>2590</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Hultsfred, Hultsfred, Sm</t>
+          <t>Tinnsjön, Tinnsjön, Sm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>540535</v>
+        <v>540587</v>
       </c>
       <c r="R20" t="n">
-        <v>6348224</v>
+        <v>6348578</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2628,10 +2628,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123653223</v>
+        <v>123652072</v>
       </c>
       <c r="B21" t="n">
-        <v>95984</v>
+        <v>5174</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2644,21 +2644,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2590</v>
+        <v>100526</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2668,13 +2668,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>540587</v>
+        <v>540512</v>
       </c>
       <c r="R21" t="n">
-        <v>6348578</v>
+        <v>6348547</v>
       </c>
       <c r="S21" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2704,6 +2704,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-03-31</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2730,10 +2735,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123652072</v>
+        <v>123648670</v>
       </c>
       <c r="B22" t="n">
-        <v>5174</v>
+        <v>92264</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2746,37 +2751,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100526</v>
+        <v>4364</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Tinnsjön, Tinnsjön, Sm</t>
+          <t>Hultsfred, Hultsfred, Sm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>540512</v>
+        <v>540535</v>
       </c>
       <c r="R22" t="n">
-        <v>6348547</v>
+        <v>6348224</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2806,11 +2811,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-03-31</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3452,6 +3452,429 @@
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>123784231</v>
+      </c>
+      <c r="B29" t="n">
+        <v>91603</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>1339</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Brandticka</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Pycnoporellus fulgens</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Tinnsjön, Tinnsjön, Sm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>540612</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6348517</v>
+      </c>
+      <c r="S29" t="n">
+        <v>15</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Hultsfred</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Virserum</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-04-05</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-04-05</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>123784690</v>
+      </c>
+      <c r="B30" t="n">
+        <v>97023</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>2606</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Klippfrullania</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Frullania tamarisci</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(L.) Dumort.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Tinnsjön, Tinnsjön, Sm</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>540591</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6348537</v>
+      </c>
+      <c r="S30" t="n">
+        <v>15</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Hultsfred</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Virserum</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-04-05</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-04-05</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>123780551</v>
+      </c>
+      <c r="B31" t="n">
+        <v>57640</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Hultsfred, Hultsfred, Sm</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>540543</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6348259</v>
+      </c>
+      <c r="S31" t="n">
+        <v>25</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Hultsfred</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Virserum</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-04-05</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-04-05</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>123781316</v>
+      </c>
+      <c r="B32" t="n">
+        <v>91253</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>73</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Veckticka</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Flavidoporia pulvinascens</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Pilát) Audet</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Hultsfred, Hultsfred, Sm</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>540550</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6348256</v>
+      </c>
+      <c r="S32" t="n">
+        <v>15</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Hultsfred</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Virserum</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-04-05</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-04-05</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>På asplåga</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 14019-2025 artfynd.xlsx
+++ b/artfynd/A 14019-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123648565</v>
+        <v>123651287</v>
       </c>
       <c r="B2" t="n">
-        <v>91003</v>
+        <v>98502</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,41 +687,41 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hultsfred, Hultsfred, Sm</t>
+          <t>Tinnsjön, Tinnsjön, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>540519</v>
+        <v>540463</v>
       </c>
       <c r="R2" t="n">
-        <v>6348230</v>
+        <v>6348492</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123652358</v>
+        <v>123653838</v>
       </c>
       <c r="B3" t="n">
-        <v>57503</v>
+        <v>98502</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>540555</v>
+        <v>540614</v>
       </c>
       <c r="R3" t="n">
-        <v>6348531</v>
+        <v>6348556</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -853,11 +853,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-31</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123651753</v>
+        <v>123649033</v>
       </c>
       <c r="B4" t="n">
-        <v>57857</v>
+        <v>57506</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -896,20 +891,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -918,24 +913,19 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Tinnsjön, Tinnsjön, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>540454</v>
+        <v>540498</v>
       </c>
       <c r="R4" t="n">
-        <v>6348509</v>
+        <v>6348264</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -965,6 +955,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-31</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123654838</v>
+        <v>123651434</v>
       </c>
       <c r="B5" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1031,13 +1026,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>540648</v>
+        <v>540454</v>
       </c>
       <c r="R5" t="n">
-        <v>6348392</v>
+        <v>6348489</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1093,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123655187</v>
+        <v>123652358</v>
       </c>
       <c r="B6" t="n">
-        <v>92264</v>
+        <v>57506</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1105,25 +1100,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>540525</v>
+        <v>540555</v>
       </c>
       <c r="R6" t="n">
-        <v>6348308</v>
+        <v>6348531</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1169,6 +1164,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-03-31</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1195,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123651343</v>
+        <v>123651593</v>
       </c>
       <c r="B7" t="n">
-        <v>100662</v>
+        <v>98502</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1207,25 +1207,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1235,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>540457</v>
+        <v>540446</v>
       </c>
       <c r="R7" t="n">
-        <v>6348499</v>
+        <v>6348497</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1297,10 +1297,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123654517</v>
+        <v>123648670</v>
       </c>
       <c r="B8" t="n">
-        <v>98396</v>
+        <v>92269</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1309,41 +1309,41 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Tinnsjön, Tinnsjön, Sm</t>
+          <t>Hultsfred, Hultsfred, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>540625</v>
+        <v>540535</v>
       </c>
       <c r="R8" t="n">
-        <v>6348461</v>
+        <v>6348224</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1399,10 +1399,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123651434</v>
+        <v>123654517</v>
       </c>
       <c r="B9" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1439,13 +1439,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>540454</v>
+        <v>540625</v>
       </c>
       <c r="R9" t="n">
-        <v>6348489</v>
+        <v>6348461</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1501,10 +1501,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123649033</v>
+        <v>123648565</v>
       </c>
       <c r="B10" t="n">
-        <v>57503</v>
+        <v>91008</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1517,37 +1517,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Tinnsjön, Tinnsjön, Sm</t>
+          <t>Hultsfred, Hultsfred, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>540498</v>
+        <v>540519</v>
       </c>
       <c r="R10" t="n">
-        <v>6348264</v>
+        <v>6348230</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1577,11 +1577,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-03-31</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1608,10 +1603,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123651999</v>
+        <v>123651201</v>
       </c>
       <c r="B11" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1648,13 +1643,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>540507</v>
+        <v>540472</v>
       </c>
       <c r="R11" t="n">
-        <v>6348554</v>
+        <v>6348468</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1713,7 +1708,7 @@
         <v>123651626</v>
       </c>
       <c r="B12" t="n">
-        <v>100662</v>
+        <v>100680</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1812,10 +1807,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123651201</v>
+        <v>123648212</v>
       </c>
       <c r="B13" t="n">
-        <v>98396</v>
+        <v>95019</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1824,41 +1819,41 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>210</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Tinnsjön, Tinnsjön, Sm</t>
+          <t>Hultsfred, Hultsfred, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>540472</v>
+        <v>540478</v>
       </c>
       <c r="R13" t="n">
-        <v>6348468</v>
+        <v>6348196</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1914,10 +1909,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123651287</v>
+        <v>123651753</v>
       </c>
       <c r="B14" t="n">
-        <v>98396</v>
+        <v>57860</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1926,41 +1921,46 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Tinnsjön, Tinnsjön, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>540463</v>
+        <v>540454</v>
       </c>
       <c r="R14" t="n">
-        <v>6348492</v>
+        <v>6348509</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2016,10 +2016,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123653838</v>
+        <v>123653223</v>
       </c>
       <c r="B15" t="n">
-        <v>98396</v>
+        <v>95991</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2028,25 +2028,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>2590</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2056,13 +2056,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>540614</v>
+        <v>540587</v>
       </c>
       <c r="R15" t="n">
-        <v>6348556</v>
+        <v>6348578</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2118,10 +2118,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123654095</v>
+        <v>123651999</v>
       </c>
       <c r="B16" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2158,13 +2158,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>540624</v>
+        <v>540507</v>
       </c>
       <c r="R16" t="n">
-        <v>6348499</v>
+        <v>6348554</v>
       </c>
       <c r="S16" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2220,10 +2220,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123650824</v>
+        <v>123652072</v>
       </c>
       <c r="B17" t="n">
-        <v>98396</v>
+        <v>5176</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2232,25 +2232,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2260,13 +2260,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>540485</v>
+        <v>540512</v>
       </c>
       <c r="R17" t="n">
-        <v>6348449</v>
+        <v>6348547</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2296,6 +2296,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-03-31</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2322,10 +2327,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123648212</v>
+        <v>123651343</v>
       </c>
       <c r="B18" t="n">
-        <v>95013</v>
+        <v>100680</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2338,37 +2343,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>210</v>
+        <v>222498</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Hultsfred, Hultsfred, Sm</t>
+          <t>Tinnsjön, Tinnsjön, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>540478</v>
+        <v>540457</v>
       </c>
       <c r="R18" t="n">
-        <v>6348196</v>
+        <v>6348499</v>
       </c>
       <c r="S18" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2424,10 +2429,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123651593</v>
+        <v>123654838</v>
       </c>
       <c r="B19" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2464,10 +2469,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>540446</v>
+        <v>540648</v>
       </c>
       <c r="R19" t="n">
-        <v>6348497</v>
+        <v>6348392</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2526,10 +2531,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123653223</v>
+        <v>123655187</v>
       </c>
       <c r="B20" t="n">
-        <v>95984</v>
+        <v>92269</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2542,21 +2547,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2590</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2566,13 +2571,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>540587</v>
+        <v>540525</v>
       </c>
       <c r="R20" t="n">
-        <v>6348578</v>
+        <v>6348308</v>
       </c>
       <c r="S20" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2628,10 +2633,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123652072</v>
+        <v>123654095</v>
       </c>
       <c r="B21" t="n">
-        <v>5174</v>
+        <v>98502</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2640,25 +2645,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2668,13 +2673,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>540512</v>
+        <v>540624</v>
       </c>
       <c r="R21" t="n">
-        <v>6348547</v>
+        <v>6348499</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2704,11 +2709,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-03-31</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2735,10 +2735,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123648670</v>
+        <v>123650824</v>
       </c>
       <c r="B22" t="n">
-        <v>92264</v>
+        <v>98502</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2747,38 +2747,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Hultsfred, Hultsfred, Sm</t>
+          <t>Tinnsjön, Tinnsjön, Sm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>540535</v>
+        <v>540485</v>
       </c>
       <c r="R22" t="n">
-        <v>6348224</v>
+        <v>6348449</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2837,10 +2837,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123678423</v>
+        <v>123676068</v>
       </c>
       <c r="B23" t="n">
-        <v>100662</v>
+        <v>97367</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2853,37 +2853,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Tinnsjön, Tinnsjön, Sm</t>
+          <t>Hultsfred, Hultsfred, Sm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>540463</v>
+        <v>540573</v>
       </c>
       <c r="R23" t="n">
-        <v>6348528</v>
+        <v>6348225</v>
       </c>
       <c r="S23" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2942,7 +2942,7 @@
         <v>123677321</v>
       </c>
       <c r="B24" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3041,10 +3041,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123677186</v>
+        <v>123678423</v>
       </c>
       <c r="B25" t="n">
-        <v>92264</v>
+        <v>100680</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3057,21 +3057,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4364</v>
+        <v>222498</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3081,13 +3081,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>540521</v>
+        <v>540463</v>
       </c>
       <c r="R25" t="n">
-        <v>6348451</v>
+        <v>6348528</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3143,10 +3143,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123676891</v>
+        <v>123677186</v>
       </c>
       <c r="B26" t="n">
-        <v>98396</v>
+        <v>92269</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3155,25 +3155,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3183,13 +3183,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>540557</v>
+        <v>540521</v>
       </c>
       <c r="R26" t="n">
-        <v>6348447</v>
+        <v>6348451</v>
       </c>
       <c r="S26" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3248,7 +3248,7 @@
         <v>123677388</v>
       </c>
       <c r="B27" t="n">
-        <v>57640</v>
+        <v>57643</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3352,10 +3352,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123676068</v>
+        <v>123676891</v>
       </c>
       <c r="B28" t="n">
-        <v>97350</v>
+        <v>98502</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3364,41 +3364,41 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Hultsfred, Hultsfred, Sm</t>
+          <t>Tinnsjön, Tinnsjön, Sm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>540573</v>
+        <v>540557</v>
       </c>
       <c r="R28" t="n">
-        <v>6348225</v>
+        <v>6348447</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3454,10 +3454,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123784231</v>
+        <v>123780551</v>
       </c>
       <c r="B29" t="n">
-        <v>91603</v>
+        <v>57643</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3466,41 +3466,46 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1339</v>
+        <v>103021</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Tinnsjön, Tinnsjön, Sm</t>
+          <t>Hultsfred, Hultsfred, Sm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>540612</v>
+        <v>540543</v>
       </c>
       <c r="R29" t="n">
-        <v>6348517</v>
+        <v>6348259</v>
       </c>
       <c r="S29" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3559,7 +3564,7 @@
         <v>123784690</v>
       </c>
       <c r="B30" t="n">
-        <v>97023</v>
+        <v>97039</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3663,10 +3668,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123780551</v>
+        <v>123784231</v>
       </c>
       <c r="B31" t="n">
-        <v>57640</v>
+        <v>91608</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3675,46 +3680,41 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>103021</v>
+        <v>1339</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Hultsfred, Hultsfred, Sm</t>
+          <t>Tinnsjön, Tinnsjön, Sm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>540543</v>
+        <v>540612</v>
       </c>
       <c r="R31" t="n">
-        <v>6348259</v>
+        <v>6348517</v>
       </c>
       <c r="S31" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3773,7 +3773,7 @@
         <v>123781316</v>
       </c>
       <c r="B32" t="n">
-        <v>91253</v>
+        <v>91258</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>

--- a/artfynd/A 14019-2025 artfynd.xlsx
+++ b/artfynd/A 14019-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123651287</v>
+        <v>123649033</v>
       </c>
       <c r="B2" t="n">
-        <v>98502</v>
+        <v>57507</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>540463</v>
+        <v>540498</v>
       </c>
       <c r="R2" t="n">
-        <v>6348492</v>
+        <v>6348264</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-03-31</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123653838</v>
+        <v>123651753</v>
       </c>
       <c r="B3" t="n">
-        <v>98502</v>
+        <v>57861</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,41 +794,46 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Tinnsjön, Tinnsjön, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>540614</v>
+        <v>540454</v>
       </c>
       <c r="R3" t="n">
-        <v>6348556</v>
+        <v>6348509</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123649033</v>
+        <v>123651201</v>
       </c>
       <c r="B4" t="n">
-        <v>57506</v>
+        <v>98504</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +901,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,13 +929,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>540498</v>
+        <v>540472</v>
       </c>
       <c r="R4" t="n">
-        <v>6348264</v>
+        <v>6348468</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -955,11 +965,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-31</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -986,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123651434</v>
+        <v>123651287</v>
       </c>
       <c r="B5" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1026,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>540454</v>
+        <v>540463</v>
       </c>
       <c r="R5" t="n">
-        <v>6348489</v>
+        <v>6348492</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123652358</v>
+        <v>123654517</v>
       </c>
       <c r="B6" t="n">
-        <v>57506</v>
+        <v>98504</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1100,25 +1105,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1128,13 +1133,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>540555</v>
+        <v>540625</v>
       </c>
       <c r="R6" t="n">
-        <v>6348531</v>
+        <v>6348461</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1164,11 +1169,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-03-31</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1195,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123651593</v>
+        <v>123653838</v>
       </c>
       <c r="B7" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1235,13 +1235,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>540446</v>
+        <v>540614</v>
       </c>
       <c r="R7" t="n">
-        <v>6348497</v>
+        <v>6348556</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1297,10 +1297,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123648670</v>
+        <v>123652358</v>
       </c>
       <c r="B8" t="n">
-        <v>92269</v>
+        <v>57507</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1309,38 +1309,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Hultsfred, Hultsfred, Sm</t>
+          <t>Tinnsjön, Tinnsjön, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>540535</v>
+        <v>540555</v>
       </c>
       <c r="R8" t="n">
-        <v>6348224</v>
+        <v>6348531</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1373,6 +1373,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-03-31</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1399,10 +1404,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123654517</v>
+        <v>123651343</v>
       </c>
       <c r="B9" t="n">
-        <v>98502</v>
+        <v>100682</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1411,25 +1416,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1439,13 +1444,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>540625</v>
+        <v>540457</v>
       </c>
       <c r="R9" t="n">
-        <v>6348461</v>
+        <v>6348499</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1501,10 +1506,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123648565</v>
+        <v>123653223</v>
       </c>
       <c r="B10" t="n">
-        <v>91008</v>
+        <v>95993</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1513,38 +1518,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5442</v>
+        <v>2590</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Hultsfred, Hultsfred, Sm</t>
+          <t>Tinnsjön, Tinnsjön, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>540519</v>
+        <v>540587</v>
       </c>
       <c r="R10" t="n">
-        <v>6348230</v>
+        <v>6348578</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1603,10 +1608,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123651201</v>
+        <v>123652072</v>
       </c>
       <c r="B11" t="n">
-        <v>98502</v>
+        <v>5176</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1615,25 +1620,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1643,13 +1648,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>540472</v>
+        <v>540512</v>
       </c>
       <c r="R11" t="n">
-        <v>6348468</v>
+        <v>6348547</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1679,6 +1684,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-03-31</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1705,10 +1715,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123651626</v>
+        <v>123651999</v>
       </c>
       <c r="B12" t="n">
-        <v>100680</v>
+        <v>98504</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1717,25 +1727,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1745,13 +1755,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>540438</v>
+        <v>540507</v>
       </c>
       <c r="R12" t="n">
-        <v>6348476</v>
+        <v>6348554</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1807,10 +1817,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123648212</v>
+        <v>123651593</v>
       </c>
       <c r="B13" t="n">
-        <v>95019</v>
+        <v>98504</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1819,41 +1829,41 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>210</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Hultsfred, Hultsfred, Sm</t>
+          <t>Tinnsjön, Tinnsjön, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>540478</v>
+        <v>540446</v>
       </c>
       <c r="R13" t="n">
-        <v>6348196</v>
+        <v>6348497</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1909,10 +1919,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123651753</v>
+        <v>123654838</v>
       </c>
       <c r="B14" t="n">
-        <v>57860</v>
+        <v>98504</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1921,46 +1931,41 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Tinnsjön, Tinnsjön, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>540454</v>
+        <v>540648</v>
       </c>
       <c r="R14" t="n">
-        <v>6348509</v>
+        <v>6348392</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2016,10 +2021,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123653223</v>
+        <v>123651434</v>
       </c>
       <c r="B15" t="n">
-        <v>95991</v>
+        <v>98504</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2028,25 +2033,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2590</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2056,13 +2061,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>540587</v>
+        <v>540454</v>
       </c>
       <c r="R15" t="n">
-        <v>6348578</v>
+        <v>6348489</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2118,10 +2123,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123651999</v>
+        <v>123651626</v>
       </c>
       <c r="B16" t="n">
-        <v>98502</v>
+        <v>100682</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2130,25 +2135,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2158,13 +2163,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>540507</v>
+        <v>540438</v>
       </c>
       <c r="R16" t="n">
-        <v>6348554</v>
+        <v>6348476</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2220,10 +2225,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123652072</v>
+        <v>123650824</v>
       </c>
       <c r="B17" t="n">
-        <v>5176</v>
+        <v>98504</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2232,25 +2237,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2260,13 +2265,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>540512</v>
+        <v>540485</v>
       </c>
       <c r="R17" t="n">
-        <v>6348547</v>
+        <v>6348449</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2296,11 +2301,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-03-31</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2327,10 +2327,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123651343</v>
+        <v>123655187</v>
       </c>
       <c r="B18" t="n">
-        <v>100680</v>
+        <v>92271</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2343,21 +2343,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>222498</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2367,10 +2367,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>540457</v>
+        <v>540525</v>
       </c>
       <c r="R18" t="n">
-        <v>6348499</v>
+        <v>6348308</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2429,10 +2429,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123654838</v>
+        <v>123654095</v>
       </c>
       <c r="B19" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2469,13 +2469,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>540648</v>
+        <v>540624</v>
       </c>
       <c r="R19" t="n">
-        <v>6348392</v>
+        <v>6348499</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2531,10 +2531,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123655187</v>
+        <v>123648565</v>
       </c>
       <c r="B20" t="n">
-        <v>92269</v>
+        <v>91010</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2543,41 +2543,41 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>5442</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Tinnsjön, Tinnsjön, Sm</t>
+          <t>Hultsfred, Hultsfred, Sm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>540525</v>
+        <v>540519</v>
       </c>
       <c r="R20" t="n">
-        <v>6348308</v>
+        <v>6348230</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2633,10 +2633,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123654095</v>
+        <v>123648670</v>
       </c>
       <c r="B21" t="n">
-        <v>98502</v>
+        <v>92271</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2645,41 +2645,41 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Tinnsjön, Tinnsjön, Sm</t>
+          <t>Hultsfred, Hultsfred, Sm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>540624</v>
+        <v>540535</v>
       </c>
       <c r="R21" t="n">
-        <v>6348499</v>
+        <v>6348224</v>
       </c>
       <c r="S21" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2735,10 +2735,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123650824</v>
+        <v>123648212</v>
       </c>
       <c r="B22" t="n">
-        <v>98502</v>
+        <v>95021</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2747,41 +2747,41 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>210</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Tinnsjön, Tinnsjön, Sm</t>
+          <t>Hultsfred, Hultsfred, Sm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>540485</v>
+        <v>540478</v>
       </c>
       <c r="R22" t="n">
-        <v>6348449</v>
+        <v>6348196</v>
       </c>
       <c r="S22" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2837,10 +2837,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123676068</v>
+        <v>123677321</v>
       </c>
       <c r="B23" t="n">
-        <v>97367</v>
+        <v>98504</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2849,41 +2849,41 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Hultsfred, Hultsfred, Sm</t>
+          <t>Tinnsjön, Tinnsjön, Sm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>540573</v>
+        <v>540504</v>
       </c>
       <c r="R23" t="n">
-        <v>6348225</v>
+        <v>6348434</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2939,10 +2939,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123677321</v>
+        <v>123676891</v>
       </c>
       <c r="B24" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2979,10 +2979,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>540504</v>
+        <v>540557</v>
       </c>
       <c r="R24" t="n">
-        <v>6348434</v>
+        <v>6348447</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3041,10 +3041,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123678423</v>
+        <v>123677186</v>
       </c>
       <c r="B25" t="n">
-        <v>100680</v>
+        <v>92271</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3057,21 +3057,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>222498</v>
+        <v>4364</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3081,13 +3081,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>540463</v>
+        <v>540521</v>
       </c>
       <c r="R25" t="n">
-        <v>6348528</v>
+        <v>6348451</v>
       </c>
       <c r="S25" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3143,10 +3143,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123677186</v>
+        <v>123678423</v>
       </c>
       <c r="B26" t="n">
-        <v>92269</v>
+        <v>100682</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3159,21 +3159,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4364</v>
+        <v>222498</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3183,13 +3183,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>540521</v>
+        <v>540463</v>
       </c>
       <c r="R26" t="n">
-        <v>6348451</v>
+        <v>6348528</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3245,10 +3245,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123677388</v>
+        <v>123676068</v>
       </c>
       <c r="B27" t="n">
-        <v>57643</v>
+        <v>97369</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3257,46 +3257,41 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103021</v>
+        <v>221945</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Tinnsjön, Tinnsjön, Sm</t>
+          <t>Hultsfred, Hultsfred, Sm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>540515</v>
+        <v>540573</v>
       </c>
       <c r="R27" t="n">
-        <v>6348462</v>
+        <v>6348225</v>
       </c>
       <c r="S27" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3352,10 +3347,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123676891</v>
+        <v>123677388</v>
       </c>
       <c r="B28" t="n">
-        <v>98502</v>
+        <v>57644</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3364,41 +3359,46 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Tinnsjön, Tinnsjön, Sm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>540557</v>
+        <v>540515</v>
       </c>
       <c r="R28" t="n">
-        <v>6348447</v>
+        <v>6348462</v>
       </c>
       <c r="S28" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3454,10 +3454,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123780551</v>
+        <v>123784690</v>
       </c>
       <c r="B29" t="n">
-        <v>57643</v>
+        <v>97041</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3466,46 +3466,45 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103021</v>
+        <v>2606</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Hultsfred, Hultsfred, Sm</t>
+          <t>Tinnsjön, Tinnsjön, Sm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>540543</v>
+        <v>540591</v>
       </c>
       <c r="R29" t="n">
-        <v>6348259</v>
+        <v>6348537</v>
       </c>
       <c r="S29" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3543,6 +3542,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3561,10 +3561,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123784690</v>
+        <v>123784231</v>
       </c>
       <c r="B30" t="n">
-        <v>97039</v>
+        <v>91610</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3577,38 +3577,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2606</v>
+        <v>1339</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Tinnsjön, Tinnsjön, Sm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>540591</v>
+        <v>540612</v>
       </c>
       <c r="R30" t="n">
-        <v>6348537</v>
+        <v>6348517</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3649,7 +3645,6 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3668,10 +3663,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123784231</v>
+        <v>123781316</v>
       </c>
       <c r="B31" t="n">
-        <v>91608</v>
+        <v>91260</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3680,38 +3675,38 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1339</v>
+        <v>73</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Veckticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Flavidoporia pulvinascens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Pilát) Audet</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Tinnsjön, Tinnsjön, Sm</t>
+          <t>Hultsfred, Hultsfred, Sm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>540612</v>
+        <v>540550</v>
       </c>
       <c r="R31" t="n">
-        <v>6348517</v>
+        <v>6348256</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3744,6 +3739,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-04-05</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>På asplåga</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3770,10 +3770,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123781316</v>
+        <v>123780551</v>
       </c>
       <c r="B32" t="n">
-        <v>91258</v>
+        <v>57644</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3786,37 +3786,42 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>73</v>
+        <v>103021</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Veckticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Flavidoporia pulvinascens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Pilát) Audet</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Hultsfred, Hultsfred, Sm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>540550</v>
+        <v>540543</v>
       </c>
       <c r="R32" t="n">
-        <v>6348256</v>
+        <v>6348259</v>
       </c>
       <c r="S32" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3846,11 +3851,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-04-05</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>På asplåga</t>
         </is>
       </c>
       <c r="AD32" t="b">

--- a/artfynd/A 14019-2025 artfynd.xlsx
+++ b/artfynd/A 14019-2025 artfynd.xlsx
@@ -1608,10 +1608,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123652072</v>
+        <v>123651999</v>
       </c>
       <c r="B11" t="n">
-        <v>5176</v>
+        <v>98504</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1620,25 +1620,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1648,10 +1648,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>540512</v>
+        <v>540507</v>
       </c>
       <c r="R11" t="n">
-        <v>6348547</v>
+        <v>6348554</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1684,11 +1684,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-03-31</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1715,7 +1710,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123651999</v>
+        <v>123651593</v>
       </c>
       <c r="B12" t="n">
         <v>98504</v>
@@ -1755,13 +1750,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>540507</v>
+        <v>540446</v>
       </c>
       <c r="R12" t="n">
-        <v>6348554</v>
+        <v>6348497</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1817,10 +1812,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123651593</v>
+        <v>123652072</v>
       </c>
       <c r="B13" t="n">
-        <v>98504</v>
+        <v>5176</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1829,25 +1824,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1857,13 +1852,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>540446</v>
+        <v>540512</v>
       </c>
       <c r="R13" t="n">
-        <v>6348497</v>
+        <v>6348547</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1893,6 +1888,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-03-31</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 14019-2025 artfynd.xlsx
+++ b/artfynd/A 14019-2025 artfynd.xlsx
@@ -1195,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123653838</v>
+        <v>123652358</v>
       </c>
       <c r="B7" t="n">
-        <v>98504</v>
+        <v>57507</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1207,25 +1207,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1235,13 +1235,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>540614</v>
+        <v>540555</v>
       </c>
       <c r="R7" t="n">
-        <v>6348556</v>
+        <v>6348531</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1271,6 +1271,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-03-31</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1297,10 +1302,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123652358</v>
+        <v>123653838</v>
       </c>
       <c r="B8" t="n">
-        <v>57507</v>
+        <v>98504</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1309,25 +1314,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1337,13 +1342,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>540555</v>
+        <v>540614</v>
       </c>
       <c r="R8" t="n">
-        <v>6348531</v>
+        <v>6348556</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1373,11 +1378,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-03-31</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 14019-2025 artfynd.xlsx
+++ b/artfynd/A 14019-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123649033</v>
+        <v>123648565</v>
       </c>
       <c r="B2" t="n">
-        <v>57507</v>
+        <v>91010</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,37 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Tinnsjön, Tinnsjön, Sm</t>
+          <t>Hultsfred, Hultsfred, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>540498</v>
+        <v>540519</v>
       </c>
       <c r="R2" t="n">
-        <v>6348264</v>
+        <v>6348230</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-03-31</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123651753</v>
+        <v>123651999</v>
       </c>
       <c r="B3" t="n">
-        <v>57861</v>
+        <v>98079</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,46 +789,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Tinnsjön, Tinnsjön, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>540454</v>
+        <v>540507</v>
       </c>
       <c r="R3" t="n">
-        <v>6348509</v>
+        <v>6348554</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -889,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123651201</v>
+        <v>123653223</v>
       </c>
       <c r="B4" t="n">
-        <v>98504</v>
+        <v>96368</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -901,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>2590</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,13 +919,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>540472</v>
+        <v>540587</v>
       </c>
       <c r="R4" t="n">
-        <v>6348468</v>
+        <v>6348578</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -991,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123651287</v>
+        <v>123651434</v>
       </c>
       <c r="B5" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1031,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>540463</v>
+        <v>540454</v>
       </c>
       <c r="R5" t="n">
-        <v>6348492</v>
+        <v>6348489</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123654517</v>
+        <v>123649033</v>
       </c>
       <c r="B6" t="n">
-        <v>98504</v>
+        <v>57507</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1105,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,13 +1123,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>540625</v>
+        <v>540498</v>
       </c>
       <c r="R6" t="n">
-        <v>6348461</v>
+        <v>6348264</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1169,6 +1159,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-03-31</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1195,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123652358</v>
+        <v>123651626</v>
       </c>
       <c r="B7" t="n">
-        <v>57507</v>
+        <v>100257</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1207,25 +1202,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1235,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>540555</v>
+        <v>540438</v>
       </c>
       <c r="R7" t="n">
-        <v>6348531</v>
+        <v>6348476</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1271,11 +1266,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-03-31</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1302,10 +1292,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123653838</v>
+        <v>123651753</v>
       </c>
       <c r="B8" t="n">
-        <v>98504</v>
+        <v>57861</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1314,41 +1304,46 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Tinnsjön, Tinnsjön, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>540614</v>
+        <v>540454</v>
       </c>
       <c r="R8" t="n">
-        <v>6348556</v>
+        <v>6348509</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1404,10 +1399,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123651343</v>
+        <v>123654095</v>
       </c>
       <c r="B9" t="n">
-        <v>100682</v>
+        <v>98079</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1416,25 +1411,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1444,13 +1439,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>540457</v>
+        <v>540624</v>
       </c>
       <c r="R9" t="n">
         <v>6348499</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1506,10 +1501,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123653223</v>
+        <v>123651343</v>
       </c>
       <c r="B10" t="n">
-        <v>95993</v>
+        <v>100257</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1522,21 +1517,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2590</v>
+        <v>222498</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1546,13 +1541,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>540587</v>
+        <v>540457</v>
       </c>
       <c r="R10" t="n">
-        <v>6348578</v>
+        <v>6348499</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1608,10 +1603,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123651999</v>
+        <v>123648670</v>
       </c>
       <c r="B11" t="n">
-        <v>98504</v>
+        <v>92271</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1620,41 +1615,41 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Tinnsjön, Tinnsjön, Sm</t>
+          <t>Hultsfred, Hultsfred, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>540507</v>
+        <v>540535</v>
       </c>
       <c r="R11" t="n">
-        <v>6348554</v>
+        <v>6348224</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1710,10 +1705,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123651593</v>
+        <v>123651287</v>
       </c>
       <c r="B12" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1750,13 +1745,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>540446</v>
+        <v>540463</v>
       </c>
       <c r="R12" t="n">
-        <v>6348497</v>
+        <v>6348492</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1812,10 +1807,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123652072</v>
+        <v>123652358</v>
       </c>
       <c r="B13" t="n">
-        <v>5176</v>
+        <v>57507</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1824,25 +1819,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1852,13 +1847,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>540512</v>
+        <v>540555</v>
       </c>
       <c r="R13" t="n">
-        <v>6348547</v>
+        <v>6348531</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1892,7 +1887,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Gnaggångar och kläckhål</t>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1919,10 +1914,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123654838</v>
+        <v>123651201</v>
       </c>
       <c r="B14" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1959,10 +1954,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>540648</v>
+        <v>540472</v>
       </c>
       <c r="R14" t="n">
-        <v>6348392</v>
+        <v>6348468</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2021,10 +2016,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123651434</v>
+        <v>123650824</v>
       </c>
       <c r="B15" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2061,13 +2056,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>540454</v>
+        <v>540485</v>
       </c>
       <c r="R15" t="n">
-        <v>6348489</v>
+        <v>6348449</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2123,10 +2118,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123651626</v>
+        <v>123654838</v>
       </c>
       <c r="B16" t="n">
-        <v>100682</v>
+        <v>98079</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2135,25 +2130,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2163,10 +2158,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>540438</v>
+        <v>540648</v>
       </c>
       <c r="R16" t="n">
-        <v>6348476</v>
+        <v>6348392</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2225,10 +2220,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123650824</v>
+        <v>123648212</v>
       </c>
       <c r="B17" t="n">
-        <v>98504</v>
+        <v>95529</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2237,41 +2232,41 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>210</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Tinnsjön, Tinnsjön, Sm</t>
+          <t>Hultsfred, Hultsfred, Sm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>540485</v>
+        <v>540478</v>
       </c>
       <c r="R17" t="n">
-        <v>6348449</v>
+        <v>6348196</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2327,10 +2322,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123655187</v>
+        <v>123653838</v>
       </c>
       <c r="B18" t="n">
-        <v>92271</v>
+        <v>98079</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2339,25 +2334,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2367,13 +2362,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>540525</v>
+        <v>540614</v>
       </c>
       <c r="R18" t="n">
-        <v>6348308</v>
+        <v>6348556</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2429,10 +2424,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123654095</v>
+        <v>123652072</v>
       </c>
       <c r="B19" t="n">
-        <v>98504</v>
+        <v>5176</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2441,25 +2436,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2469,13 +2464,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>540624</v>
+        <v>540512</v>
       </c>
       <c r="R19" t="n">
-        <v>6348499</v>
+        <v>6348547</v>
       </c>
       <c r="S19" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2505,6 +2500,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-03-31</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2531,10 +2531,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123648565</v>
+        <v>123651593</v>
       </c>
       <c r="B20" t="n">
-        <v>91010</v>
+        <v>98079</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2543,41 +2543,41 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Hultsfred, Hultsfred, Sm</t>
+          <t>Tinnsjön, Tinnsjön, Sm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>540519</v>
+        <v>540446</v>
       </c>
       <c r="R20" t="n">
-        <v>6348230</v>
+        <v>6348497</v>
       </c>
       <c r="S20" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2633,10 +2633,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123648670</v>
+        <v>123654517</v>
       </c>
       <c r="B21" t="n">
-        <v>92271</v>
+        <v>98079</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2645,41 +2645,41 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Hultsfred, Hultsfred, Sm</t>
+          <t>Tinnsjön, Tinnsjön, Sm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>540535</v>
+        <v>540625</v>
       </c>
       <c r="R21" t="n">
-        <v>6348224</v>
+        <v>6348461</v>
       </c>
       <c r="S21" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2735,10 +2735,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123648212</v>
+        <v>123655187</v>
       </c>
       <c r="B22" t="n">
-        <v>95021</v>
+        <v>92271</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2751,37 +2751,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>210</v>
+        <v>4364</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Hultsfred, Hultsfred, Sm</t>
+          <t>Tinnsjön, Tinnsjön, Sm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>540478</v>
+        <v>540525</v>
       </c>
       <c r="R22" t="n">
-        <v>6348196</v>
+        <v>6348308</v>
       </c>
       <c r="S22" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2837,10 +2837,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123677321</v>
+        <v>123677388</v>
       </c>
       <c r="B23" t="n">
-        <v>98504</v>
+        <v>57644</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2849,41 +2849,46 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Tinnsjön, Tinnsjön, Sm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>540504</v>
+        <v>540515</v>
       </c>
       <c r="R23" t="n">
-        <v>6348434</v>
+        <v>6348462</v>
       </c>
       <c r="S23" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2939,10 +2944,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123676891</v>
+        <v>123677321</v>
       </c>
       <c r="B24" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2979,10 +2984,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>540557</v>
+        <v>540504</v>
       </c>
       <c r="R24" t="n">
-        <v>6348447</v>
+        <v>6348434</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3041,10 +3046,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123677186</v>
+        <v>123676068</v>
       </c>
       <c r="B25" t="n">
-        <v>92271</v>
+        <v>96957</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3057,34 +3062,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4364</v>
+        <v>221945</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Tinnsjön, Tinnsjön, Sm</t>
+          <t>Hultsfred, Hultsfred, Sm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>540521</v>
+        <v>540573</v>
       </c>
       <c r="R25" t="n">
-        <v>6348451</v>
+        <v>6348225</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3143,10 +3148,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123678423</v>
+        <v>123677186</v>
       </c>
       <c r="B26" t="n">
-        <v>100682</v>
+        <v>92271</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3159,21 +3164,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>222498</v>
+        <v>4364</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3183,13 +3188,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>540463</v>
+        <v>540521</v>
       </c>
       <c r="R26" t="n">
-        <v>6348528</v>
+        <v>6348451</v>
       </c>
       <c r="S26" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3245,10 +3250,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123676068</v>
+        <v>123678423</v>
       </c>
       <c r="B27" t="n">
-        <v>97369</v>
+        <v>100257</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3261,37 +3266,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221945</v>
+        <v>222498</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Hultsfred, Hultsfred, Sm</t>
+          <t>Tinnsjön, Tinnsjön, Sm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>540573</v>
+        <v>540463</v>
       </c>
       <c r="R27" t="n">
-        <v>6348225</v>
+        <v>6348528</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3347,10 +3352,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123677388</v>
+        <v>123676891</v>
       </c>
       <c r="B28" t="n">
-        <v>57644</v>
+        <v>98079</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3359,46 +3364,41 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Tinnsjön, Tinnsjön, Sm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>540515</v>
+        <v>540557</v>
       </c>
       <c r="R28" t="n">
-        <v>6348462</v>
+        <v>6348447</v>
       </c>
       <c r="S28" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3454,10 +3454,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123784690</v>
+        <v>123781316</v>
       </c>
       <c r="B29" t="n">
-        <v>97041</v>
+        <v>91260</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3466,42 +3466,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2606</v>
+        <v>73</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Veckticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Flavidoporia pulvinascens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Pilát) Audet</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Tinnsjön, Tinnsjön, Sm</t>
+          <t>Hultsfred, Hultsfred, Sm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>540591</v>
+        <v>540550</v>
       </c>
       <c r="R29" t="n">
-        <v>6348537</v>
+        <v>6348256</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3536,13 +3532,17 @@
           <t>2025-04-05</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>På asplåga</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3561,10 +3561,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123784231</v>
+        <v>123784690</v>
       </c>
       <c r="B30" t="n">
-        <v>91610</v>
+        <v>96759</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3577,34 +3577,38 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1339</v>
+        <v>2606</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Tinnsjön, Tinnsjön, Sm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>540612</v>
+        <v>540591</v>
       </c>
       <c r="R30" t="n">
-        <v>6348517</v>
+        <v>6348537</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3645,6 +3649,7 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3663,10 +3668,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123781316</v>
+        <v>123784231</v>
       </c>
       <c r="B31" t="n">
-        <v>91260</v>
+        <v>91610</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3675,38 +3680,38 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>73</v>
+        <v>1339</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Veckticka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Flavidoporia pulvinascens</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Pilát) Audet</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Hultsfred, Hultsfred, Sm</t>
+          <t>Tinnsjön, Tinnsjön, Sm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>540550</v>
+        <v>540612</v>
       </c>
       <c r="R31" t="n">
-        <v>6348256</v>
+        <v>6348517</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3739,11 +3744,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-04-05</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>På asplåga</t>
         </is>
       </c>
       <c r="AD31" t="b">

--- a/artfynd/A 14019-2025 artfynd.xlsx
+++ b/artfynd/A 14019-2025 artfynd.xlsx
@@ -1292,10 +1292,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123651753</v>
+        <v>123654095</v>
       </c>
       <c r="B8" t="n">
-        <v>57861</v>
+        <v>98079</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1304,46 +1304,41 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Tinnsjön, Tinnsjön, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>540454</v>
+        <v>540624</v>
       </c>
       <c r="R8" t="n">
-        <v>6348509</v>
+        <v>6348499</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1399,10 +1394,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123654095</v>
+        <v>123651753</v>
       </c>
       <c r="B9" t="n">
-        <v>98079</v>
+        <v>57861</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1411,41 +1406,46 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Tinnsjön, Tinnsjön, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>540624</v>
+        <v>540454</v>
       </c>
       <c r="R9" t="n">
-        <v>6348499</v>
+        <v>6348509</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>

--- a/artfynd/A 14019-2025 artfynd.xlsx
+++ b/artfynd/A 14019-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123648565</v>
+        <v>123651593</v>
       </c>
       <c r="B2" t="n">
-        <v>91010</v>
+        <v>98079</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,41 +687,41 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hultsfred, Hultsfred, Sm</t>
+          <t>Tinnsjön, Tinnsjön, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>540519</v>
+        <v>540446</v>
       </c>
       <c r="R2" t="n">
-        <v>6348230</v>
+        <v>6348497</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123651999</v>
+        <v>123651343</v>
       </c>
       <c r="B3" t="n">
-        <v>98079</v>
+        <v>100257</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>540507</v>
+        <v>540457</v>
       </c>
       <c r="R3" t="n">
-        <v>6348554</v>
+        <v>6348499</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123653223</v>
+        <v>123654517</v>
       </c>
       <c r="B4" t="n">
-        <v>96368</v>
+        <v>98079</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2590</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>540587</v>
+        <v>540625</v>
       </c>
       <c r="R4" t="n">
-        <v>6348578</v>
+        <v>6348461</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123651434</v>
+        <v>123652358</v>
       </c>
       <c r="B5" t="n">
-        <v>98079</v>
+        <v>57507</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,13 +1021,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>540454</v>
+        <v>540555</v>
       </c>
       <c r="R5" t="n">
-        <v>6348489</v>
+        <v>6348531</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1057,6 +1057,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-03-31</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1083,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123649033</v>
+        <v>123651626</v>
       </c>
       <c r="B6" t="n">
-        <v>57507</v>
+        <v>100257</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1100,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,13 +1128,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>540498</v>
+        <v>540438</v>
       </c>
       <c r="R6" t="n">
-        <v>6348264</v>
+        <v>6348476</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1159,11 +1164,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-03-31</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1190,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123651626</v>
+        <v>123653223</v>
       </c>
       <c r="B7" t="n">
-        <v>100257</v>
+        <v>96368</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1206,21 +1206,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222498</v>
+        <v>2590</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1230,13 +1230,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>540438</v>
+        <v>540587</v>
       </c>
       <c r="R7" t="n">
-        <v>6348476</v>
+        <v>6348578</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123654095</v>
+        <v>123651287</v>
       </c>
       <c r="B8" t="n">
         <v>98079</v>
@@ -1332,13 +1332,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>540624</v>
+        <v>540463</v>
       </c>
       <c r="R8" t="n">
-        <v>6348499</v>
+        <v>6348492</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1394,10 +1394,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123651753</v>
+        <v>123648670</v>
       </c>
       <c r="B9" t="n">
-        <v>57861</v>
+        <v>92271</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1410,42 +1410,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103015</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Tinnsjön, Tinnsjön, Sm</t>
+          <t>Hultsfred, Hultsfred, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>540454</v>
+        <v>540535</v>
       </c>
       <c r="R9" t="n">
-        <v>6348509</v>
+        <v>6348224</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1501,10 +1496,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123651343</v>
+        <v>123648565</v>
       </c>
       <c r="B10" t="n">
-        <v>100257</v>
+        <v>91010</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1513,41 +1508,41 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222498</v>
+        <v>5442</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Tinnsjön, Tinnsjön, Sm</t>
+          <t>Hultsfred, Hultsfred, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>540457</v>
+        <v>540519</v>
       </c>
       <c r="R10" t="n">
-        <v>6348499</v>
+        <v>6348230</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1603,10 +1598,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123648670</v>
+        <v>123654838</v>
       </c>
       <c r="B11" t="n">
-        <v>92271</v>
+        <v>98079</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1615,38 +1610,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Hultsfred, Hultsfred, Sm</t>
+          <t>Tinnsjön, Tinnsjön, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>540535</v>
+        <v>540648</v>
       </c>
       <c r="R11" t="n">
-        <v>6348224</v>
+        <v>6348392</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1705,7 +1700,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123651287</v>
+        <v>123651201</v>
       </c>
       <c r="B12" t="n">
         <v>98079</v>
@@ -1745,13 +1740,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>540463</v>
+        <v>540472</v>
       </c>
       <c r="R12" t="n">
-        <v>6348492</v>
+        <v>6348468</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1807,7 +1802,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123652358</v>
+        <v>123649033</v>
       </c>
       <c r="B13" t="n">
         <v>57507</v>
@@ -1847,13 +1842,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>540555</v>
+        <v>540498</v>
       </c>
       <c r="R13" t="n">
-        <v>6348531</v>
+        <v>6348264</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1914,7 +1909,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123651201</v>
+        <v>123651999</v>
       </c>
       <c r="B14" t="n">
         <v>98079</v>
@@ -1954,13 +1949,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>540472</v>
+        <v>540507</v>
       </c>
       <c r="R14" t="n">
-        <v>6348468</v>
+        <v>6348554</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2016,10 +2011,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123650824</v>
+        <v>123652072</v>
       </c>
       <c r="B15" t="n">
-        <v>98079</v>
+        <v>5176</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2028,25 +2023,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2056,13 +2051,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>540485</v>
+        <v>540512</v>
       </c>
       <c r="R15" t="n">
-        <v>6348449</v>
+        <v>6348547</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2092,6 +2087,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-03-31</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2118,10 +2118,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123654838</v>
+        <v>123648212</v>
       </c>
       <c r="B16" t="n">
-        <v>98079</v>
+        <v>95529</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2130,41 +2130,41 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>210</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Tinnsjön, Tinnsjön, Sm</t>
+          <t>Hultsfred, Hultsfred, Sm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>540648</v>
+        <v>540478</v>
       </c>
       <c r="R16" t="n">
-        <v>6348392</v>
+        <v>6348196</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2220,10 +2220,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123648212</v>
+        <v>123651434</v>
       </c>
       <c r="B17" t="n">
-        <v>95529</v>
+        <v>98079</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2232,41 +2232,41 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>210</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Hultsfred, Hultsfred, Sm</t>
+          <t>Tinnsjön, Tinnsjön, Sm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>540478</v>
+        <v>540454</v>
       </c>
       <c r="R17" t="n">
-        <v>6348196</v>
+        <v>6348489</v>
       </c>
       <c r="S17" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2322,7 +2322,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123653838</v>
+        <v>123654095</v>
       </c>
       <c r="B18" t="n">
         <v>98079</v>
@@ -2362,13 +2362,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>540614</v>
+        <v>540624</v>
       </c>
       <c r="R18" t="n">
-        <v>6348556</v>
+        <v>6348499</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2424,10 +2424,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123652072</v>
+        <v>123653838</v>
       </c>
       <c r="B19" t="n">
-        <v>5176</v>
+        <v>98079</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2436,25 +2436,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2464,10 +2464,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>540512</v>
+        <v>540614</v>
       </c>
       <c r="R19" t="n">
-        <v>6348547</v>
+        <v>6348556</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2500,11 +2500,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-03-31</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2531,7 +2526,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123651593</v>
+        <v>123650824</v>
       </c>
       <c r="B20" t="n">
         <v>98079</v>
@@ -2571,10 +2566,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>540446</v>
+        <v>540485</v>
       </c>
       <c r="R20" t="n">
-        <v>6348497</v>
+        <v>6348449</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2633,10 +2628,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123654517</v>
+        <v>123655187</v>
       </c>
       <c r="B21" t="n">
-        <v>98079</v>
+        <v>92271</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2645,25 +2640,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2673,13 +2668,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>540625</v>
+        <v>540525</v>
       </c>
       <c r="R21" t="n">
-        <v>6348461</v>
+        <v>6348308</v>
       </c>
       <c r="S21" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2735,10 +2730,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123655187</v>
+        <v>123651753</v>
       </c>
       <c r="B22" t="n">
-        <v>92271</v>
+        <v>57861</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2751,37 +2746,42 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4364</v>
+        <v>103015</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Tinnsjön, Tinnsjön, Sm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>540525</v>
+        <v>540454</v>
       </c>
       <c r="R22" t="n">
-        <v>6348308</v>
+        <v>6348509</v>
       </c>
       <c r="S22" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2837,10 +2837,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123677388</v>
+        <v>123677321</v>
       </c>
       <c r="B23" t="n">
-        <v>57644</v>
+        <v>98079</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2849,46 +2849,41 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Tinnsjön, Tinnsjön, Sm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>540515</v>
+        <v>540504</v>
       </c>
       <c r="R23" t="n">
-        <v>6348462</v>
+        <v>6348434</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2944,10 +2939,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123677321</v>
+        <v>123677388</v>
       </c>
       <c r="B24" t="n">
-        <v>98079</v>
+        <v>57644</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2956,41 +2951,46 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Tinnsjön, Tinnsjön, Sm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>540504</v>
+        <v>540515</v>
       </c>
       <c r="R24" t="n">
-        <v>6348434</v>
+        <v>6348462</v>
       </c>
       <c r="S24" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3148,10 +3148,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123677186</v>
+        <v>123676891</v>
       </c>
       <c r="B26" t="n">
-        <v>92271</v>
+        <v>98079</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3160,25 +3160,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3188,13 +3188,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>540521</v>
+        <v>540557</v>
       </c>
       <c r="R26" t="n">
-        <v>6348451</v>
+        <v>6348447</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3352,10 +3352,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123676891</v>
+        <v>123677186</v>
       </c>
       <c r="B28" t="n">
-        <v>98079</v>
+        <v>92271</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3364,25 +3364,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3392,13 +3392,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>540557</v>
+        <v>540521</v>
       </c>
       <c r="R28" t="n">
-        <v>6348447</v>
+        <v>6348451</v>
       </c>
       <c r="S28" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3454,10 +3454,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123781316</v>
+        <v>123780551</v>
       </c>
       <c r="B29" t="n">
-        <v>91260</v>
+        <v>57644</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3470,37 +3470,42 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>73</v>
+        <v>103021</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Veckticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Flavidoporia pulvinascens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Pilát) Audet</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Hultsfred, Hultsfred, Sm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>540550</v>
+        <v>540543</v>
       </c>
       <c r="R29" t="n">
-        <v>6348256</v>
+        <v>6348259</v>
       </c>
       <c r="S29" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3530,11 +3535,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-04-05</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>På asplåga</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3561,10 +3561,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123784690</v>
+        <v>123784231</v>
       </c>
       <c r="B30" t="n">
-        <v>96759</v>
+        <v>91610</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3577,38 +3577,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2606</v>
+        <v>1339</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Tinnsjön, Tinnsjön, Sm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>540591</v>
+        <v>540612</v>
       </c>
       <c r="R30" t="n">
-        <v>6348537</v>
+        <v>6348517</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3649,7 +3645,6 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3668,10 +3663,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123784231</v>
+        <v>123781316</v>
       </c>
       <c r="B31" t="n">
-        <v>91610</v>
+        <v>91260</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3680,38 +3675,38 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1339</v>
+        <v>73</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Veckticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Flavidoporia pulvinascens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Pilát) Audet</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Tinnsjön, Tinnsjön, Sm</t>
+          <t>Hultsfred, Hultsfred, Sm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>540612</v>
+        <v>540550</v>
       </c>
       <c r="R31" t="n">
-        <v>6348517</v>
+        <v>6348256</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3744,6 +3739,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-04-05</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>På asplåga</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3770,10 +3770,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123780551</v>
+        <v>123784690</v>
       </c>
       <c r="B32" t="n">
-        <v>57644</v>
+        <v>96759</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3782,46 +3782,45 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>103021</v>
+        <v>2606</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Hultsfred, Hultsfred, Sm</t>
+          <t>Tinnsjön, Tinnsjön, Sm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>540543</v>
+        <v>540591</v>
       </c>
       <c r="R32" t="n">
-        <v>6348259</v>
+        <v>6348537</v>
       </c>
       <c r="S32" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3859,6 +3858,7 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 14019-2025 artfynd.xlsx
+++ b/artfynd/A 14019-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123651593</v>
+        <v>123648565</v>
       </c>
       <c r="B2" t="n">
-        <v>98079</v>
+        <v>91010</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,41 +687,41 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Tinnsjön, Tinnsjön, Sm</t>
+          <t>Hultsfred, Hultsfred, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>540446</v>
+        <v>540519</v>
       </c>
       <c r="R2" t="n">
-        <v>6348497</v>
+        <v>6348230</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123651343</v>
+        <v>123651593</v>
       </c>
       <c r="B3" t="n">
-        <v>100257</v>
+        <v>98079</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>540457</v>
+        <v>540446</v>
       </c>
       <c r="R3" t="n">
-        <v>6348499</v>
+        <v>6348497</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123654517</v>
+        <v>123655187</v>
       </c>
       <c r="B4" t="n">
-        <v>98079</v>
+        <v>92271</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>540625</v>
+        <v>540525</v>
       </c>
       <c r="R4" t="n">
-        <v>6348461</v>
+        <v>6348308</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123652358</v>
+        <v>123651434</v>
       </c>
       <c r="B5" t="n">
-        <v>57507</v>
+        <v>98079</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,13 +1021,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>540555</v>
+        <v>540454</v>
       </c>
       <c r="R5" t="n">
-        <v>6348531</v>
+        <v>6348489</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1057,11 +1057,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-03-31</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1088,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123651626</v>
+        <v>123648670</v>
       </c>
       <c r="B6" t="n">
-        <v>100257</v>
+        <v>92271</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1104,34 +1099,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222498</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Tinnsjön, Tinnsjön, Sm</t>
+          <t>Hultsfred, Hultsfred, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>540438</v>
+        <v>540535</v>
       </c>
       <c r="R6" t="n">
-        <v>6348476</v>
+        <v>6348224</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1190,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123653223</v>
+        <v>123651201</v>
       </c>
       <c r="B7" t="n">
-        <v>96368</v>
+        <v>98079</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1202,25 +1197,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2590</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1230,13 +1225,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>540587</v>
+        <v>540472</v>
       </c>
       <c r="R7" t="n">
-        <v>6348578</v>
+        <v>6348468</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1292,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123651287</v>
+        <v>123649033</v>
       </c>
       <c r="B8" t="n">
-        <v>98079</v>
+        <v>57507</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1304,25 +1299,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1332,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>540463</v>
+        <v>540498</v>
       </c>
       <c r="R8" t="n">
-        <v>6348492</v>
+        <v>6348264</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1368,6 +1363,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-03-31</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1394,10 +1394,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123648670</v>
+        <v>123651626</v>
       </c>
       <c r="B9" t="n">
-        <v>92271</v>
+        <v>100257</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1410,34 +1410,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>222498</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Hultsfred, Hultsfred, Sm</t>
+          <t>Tinnsjön, Tinnsjön, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>540535</v>
+        <v>540438</v>
       </c>
       <c r="R9" t="n">
-        <v>6348224</v>
+        <v>6348476</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1496,10 +1496,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123648565</v>
+        <v>123652072</v>
       </c>
       <c r="B10" t="n">
-        <v>91010</v>
+        <v>5176</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1508,41 +1508,41 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5442</v>
+        <v>100526</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Hultsfred, Hultsfred, Sm</t>
+          <t>Tinnsjön, Tinnsjön, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>540519</v>
+        <v>540512</v>
       </c>
       <c r="R10" t="n">
-        <v>6348230</v>
+        <v>6348547</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1572,6 +1572,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-03-31</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1598,10 +1603,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123654838</v>
+        <v>123653223</v>
       </c>
       <c r="B11" t="n">
-        <v>98079</v>
+        <v>96368</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1610,25 +1615,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>2590</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1638,13 +1643,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>540648</v>
+        <v>540587</v>
       </c>
       <c r="R11" t="n">
-        <v>6348392</v>
+        <v>6348578</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1700,7 +1705,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123651201</v>
+        <v>123654517</v>
       </c>
       <c r="B12" t="n">
         <v>98079</v>
@@ -1740,13 +1745,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>540472</v>
+        <v>540625</v>
       </c>
       <c r="R12" t="n">
-        <v>6348468</v>
+        <v>6348461</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1802,10 +1807,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123649033</v>
+        <v>123648212</v>
       </c>
       <c r="B13" t="n">
-        <v>57507</v>
+        <v>95529</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1814,41 +1819,41 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>210</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Tinnsjön, Tinnsjön, Sm</t>
+          <t>Hultsfred, Hultsfred, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>540498</v>
+        <v>540478</v>
       </c>
       <c r="R13" t="n">
-        <v>6348264</v>
+        <v>6348196</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1878,11 +1883,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-03-31</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1909,7 +1909,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123651999</v>
+        <v>123653838</v>
       </c>
       <c r="B14" t="n">
         <v>98079</v>
@@ -1949,10 +1949,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>540507</v>
+        <v>540614</v>
       </c>
       <c r="R14" t="n">
-        <v>6348554</v>
+        <v>6348556</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2011,10 +2011,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123652072</v>
+        <v>123651287</v>
       </c>
       <c r="B15" t="n">
-        <v>5176</v>
+        <v>98079</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2023,25 +2023,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2051,10 +2051,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>540512</v>
+        <v>540463</v>
       </c>
       <c r="R15" t="n">
-        <v>6348547</v>
+        <v>6348492</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2087,11 +2087,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-03-31</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2118,10 +2113,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123648212</v>
+        <v>123652358</v>
       </c>
       <c r="B16" t="n">
-        <v>95529</v>
+        <v>57507</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2130,41 +2125,41 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>210</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Hultsfred, Hultsfred, Sm</t>
+          <t>Tinnsjön, Tinnsjön, Sm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>540478</v>
+        <v>540555</v>
       </c>
       <c r="R16" t="n">
-        <v>6348196</v>
+        <v>6348531</v>
       </c>
       <c r="S16" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2194,6 +2189,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-03-31</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2220,10 +2220,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123651434</v>
+        <v>123651343</v>
       </c>
       <c r="B17" t="n">
-        <v>98079</v>
+        <v>100257</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2232,25 +2232,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2260,13 +2260,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>540454</v>
+        <v>540457</v>
       </c>
       <c r="R17" t="n">
-        <v>6348489</v>
+        <v>6348499</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2322,7 +2322,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123654095</v>
+        <v>123650824</v>
       </c>
       <c r="B18" t="n">
         <v>98079</v>
@@ -2362,13 +2362,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>540624</v>
+        <v>540485</v>
       </c>
       <c r="R18" t="n">
-        <v>6348499</v>
+        <v>6348449</v>
       </c>
       <c r="S18" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2424,7 +2424,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123653838</v>
+        <v>123654838</v>
       </c>
       <c r="B19" t="n">
         <v>98079</v>
@@ -2464,13 +2464,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>540614</v>
+        <v>540648</v>
       </c>
       <c r="R19" t="n">
-        <v>6348556</v>
+        <v>6348392</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2526,7 +2526,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123650824</v>
+        <v>123651999</v>
       </c>
       <c r="B20" t="n">
         <v>98079</v>
@@ -2566,13 +2566,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>540485</v>
+        <v>540507</v>
       </c>
       <c r="R20" t="n">
-        <v>6348449</v>
+        <v>6348554</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2628,10 +2628,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123655187</v>
+        <v>123651753</v>
       </c>
       <c r="B21" t="n">
-        <v>92271</v>
+        <v>57861</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2644,37 +2644,42 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>103015</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Tinnsjön, Tinnsjön, Sm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>540525</v>
+        <v>540454</v>
       </c>
       <c r="R21" t="n">
-        <v>6348308</v>
+        <v>6348509</v>
       </c>
       <c r="S21" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2730,10 +2735,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123651753</v>
+        <v>123654095</v>
       </c>
       <c r="B22" t="n">
-        <v>57861</v>
+        <v>98079</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2742,46 +2747,41 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Tinnsjön, Tinnsjön, Sm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>540454</v>
+        <v>540624</v>
       </c>
       <c r="R22" t="n">
-        <v>6348509</v>
+        <v>6348499</v>
       </c>
       <c r="S22" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2837,10 +2837,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123677321</v>
+        <v>123677186</v>
       </c>
       <c r="B23" t="n">
-        <v>98079</v>
+        <v>92271</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2849,25 +2849,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2877,13 +2877,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>540504</v>
+        <v>540521</v>
       </c>
       <c r="R23" t="n">
-        <v>6348434</v>
+        <v>6348451</v>
       </c>
       <c r="S23" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2939,10 +2939,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123677388</v>
+        <v>123677321</v>
       </c>
       <c r="B24" t="n">
-        <v>57644</v>
+        <v>98079</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2951,46 +2951,41 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Tinnsjön, Tinnsjön, Sm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>540515</v>
+        <v>540504</v>
       </c>
       <c r="R24" t="n">
-        <v>6348462</v>
+        <v>6348434</v>
       </c>
       <c r="S24" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3046,10 +3041,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123676068</v>
+        <v>123676891</v>
       </c>
       <c r="B25" t="n">
-        <v>96957</v>
+        <v>98079</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3058,41 +3053,41 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Hultsfred, Hultsfred, Sm</t>
+          <t>Tinnsjön, Tinnsjön, Sm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>540573</v>
+        <v>540557</v>
       </c>
       <c r="R25" t="n">
-        <v>6348225</v>
+        <v>6348447</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3148,10 +3143,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123676891</v>
+        <v>123678423</v>
       </c>
       <c r="B26" t="n">
-        <v>98079</v>
+        <v>100257</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3160,25 +3155,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3188,13 +3183,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>540557</v>
+        <v>540463</v>
       </c>
       <c r="R26" t="n">
-        <v>6348447</v>
+        <v>6348528</v>
       </c>
       <c r="S26" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3250,10 +3245,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123678423</v>
+        <v>123676068</v>
       </c>
       <c r="B27" t="n">
-        <v>100257</v>
+        <v>96957</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3266,37 +3261,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Tinnsjön, Tinnsjön, Sm</t>
+          <t>Hultsfred, Hultsfred, Sm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>540463</v>
+        <v>540573</v>
       </c>
       <c r="R27" t="n">
-        <v>6348528</v>
+        <v>6348225</v>
       </c>
       <c r="S27" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3352,10 +3347,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123677186</v>
+        <v>123677388</v>
       </c>
       <c r="B28" t="n">
-        <v>92271</v>
+        <v>57644</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3364,41 +3359,46 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Tinnsjön, Tinnsjön, Sm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>540521</v>
+        <v>540515</v>
       </c>
       <c r="R28" t="n">
-        <v>6348451</v>
+        <v>6348462</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3454,10 +3454,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123780551</v>
+        <v>123784231</v>
       </c>
       <c r="B29" t="n">
-        <v>57644</v>
+        <v>91610</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3466,46 +3466,41 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103021</v>
+        <v>1339</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Hultsfred, Hultsfred, Sm</t>
+          <t>Tinnsjön, Tinnsjön, Sm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>540543</v>
+        <v>540612</v>
       </c>
       <c r="R29" t="n">
-        <v>6348259</v>
+        <v>6348517</v>
       </c>
       <c r="S29" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3561,10 +3556,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123784231</v>
+        <v>123784690</v>
       </c>
       <c r="B30" t="n">
-        <v>91610</v>
+        <v>96759</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3577,34 +3572,38 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1339</v>
+        <v>2606</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Tinnsjön, Tinnsjön, Sm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>540612</v>
+        <v>540591</v>
       </c>
       <c r="R30" t="n">
-        <v>6348517</v>
+        <v>6348537</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3645,6 +3644,7 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3770,10 +3770,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123784690</v>
+        <v>123780551</v>
       </c>
       <c r="B32" t="n">
-        <v>96759</v>
+        <v>57644</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3782,45 +3782,46 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2606</v>
+        <v>103021</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Tinnsjön, Tinnsjön, Sm</t>
+          <t>Hultsfred, Hultsfred, Sm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>540591</v>
+        <v>540543</v>
       </c>
       <c r="R32" t="n">
-        <v>6348537</v>
+        <v>6348259</v>
       </c>
       <c r="S32" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3858,7 +3859,6 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 14019-2025 artfynd.xlsx
+++ b/artfynd/A 14019-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123648565</v>
+        <v>123649033</v>
       </c>
       <c r="B2" t="n">
-        <v>91010</v>
+        <v>57507</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,37 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hultsfred, Hultsfred, Sm</t>
+          <t>Tinnsjön, Tinnsjön, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>540519</v>
+        <v>540498</v>
       </c>
       <c r="R2" t="n">
-        <v>6348230</v>
+        <v>6348264</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -751,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-03-31</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123651593</v>
+        <v>123648670</v>
       </c>
       <c r="B3" t="n">
-        <v>98079</v>
+        <v>92271</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,38 +794,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Tinnsjön, Tinnsjön, Sm</t>
+          <t>Hultsfred, Hultsfred, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>540446</v>
+        <v>540535</v>
       </c>
       <c r="R3" t="n">
-        <v>6348497</v>
+        <v>6348224</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -879,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123655187</v>
+        <v>123651287</v>
       </c>
       <c r="B4" t="n">
-        <v>92271</v>
+        <v>98079</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +896,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,13 +924,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>540525</v>
+        <v>540463</v>
       </c>
       <c r="R4" t="n">
-        <v>6348308</v>
+        <v>6348492</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -981,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123651434</v>
+        <v>123651343</v>
       </c>
       <c r="B5" t="n">
-        <v>98079</v>
+        <v>100257</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +998,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,13 +1026,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>540454</v>
+        <v>540457</v>
       </c>
       <c r="R5" t="n">
-        <v>6348489</v>
+        <v>6348499</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1083,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123648670</v>
+        <v>123648212</v>
       </c>
       <c r="B6" t="n">
-        <v>92271</v>
+        <v>95529</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1104,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>210</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,13 +1128,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>540535</v>
+        <v>540478</v>
       </c>
       <c r="R6" t="n">
-        <v>6348224</v>
+        <v>6348196</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1185,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123651201</v>
+        <v>123652358</v>
       </c>
       <c r="B7" t="n">
-        <v>98079</v>
+        <v>57507</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,25 +1202,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>540472</v>
+        <v>540555</v>
       </c>
       <c r="R7" t="n">
-        <v>6348468</v>
+        <v>6348531</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1261,6 +1266,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-03-31</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1287,10 +1297,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123649033</v>
+        <v>123651626</v>
       </c>
       <c r="B8" t="n">
-        <v>57507</v>
+        <v>100257</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1299,25 +1309,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,13 +1337,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>540498</v>
+        <v>540438</v>
       </c>
       <c r="R8" t="n">
-        <v>6348264</v>
+        <v>6348476</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1363,11 +1373,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-03-31</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1394,10 +1399,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123651626</v>
+        <v>123648565</v>
       </c>
       <c r="B9" t="n">
-        <v>100257</v>
+        <v>91010</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1406,41 +1411,41 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222498</v>
+        <v>5442</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Tinnsjön, Tinnsjön, Sm</t>
+          <t>Hultsfred, Hultsfred, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>540438</v>
+        <v>540519</v>
       </c>
       <c r="R9" t="n">
-        <v>6348476</v>
+        <v>6348230</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1603,10 +1608,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123653223</v>
+        <v>123651434</v>
       </c>
       <c r="B11" t="n">
-        <v>96368</v>
+        <v>98079</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1615,25 +1620,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2590</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1643,13 +1648,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>540587</v>
+        <v>540454</v>
       </c>
       <c r="R11" t="n">
-        <v>6348578</v>
+        <v>6348489</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1705,10 +1710,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123654517</v>
+        <v>123653223</v>
       </c>
       <c r="B12" t="n">
-        <v>98079</v>
+        <v>96368</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1717,25 +1722,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>2590</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1745,10 +1750,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>540625</v>
+        <v>540587</v>
       </c>
       <c r="R12" t="n">
-        <v>6348461</v>
+        <v>6348578</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1807,10 +1812,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123648212</v>
+        <v>123651753</v>
       </c>
       <c r="B13" t="n">
-        <v>95529</v>
+        <v>57861</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1823,37 +1828,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>210</v>
+        <v>103015</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Hultsfred, Hultsfred, Sm</t>
+          <t>Tinnsjön, Tinnsjön, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>540478</v>
+        <v>540454</v>
       </c>
       <c r="R13" t="n">
-        <v>6348196</v>
+        <v>6348509</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1909,7 +1919,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123653838</v>
+        <v>123654095</v>
       </c>
       <c r="B14" t="n">
         <v>98079</v>
@@ -1949,13 +1959,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>540614</v>
+        <v>540624</v>
       </c>
       <c r="R14" t="n">
-        <v>6348556</v>
+        <v>6348499</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2011,7 +2021,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123651287</v>
+        <v>123651999</v>
       </c>
       <c r="B15" t="n">
         <v>98079</v>
@@ -2051,10 +2061,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>540463</v>
+        <v>540507</v>
       </c>
       <c r="R15" t="n">
-        <v>6348492</v>
+        <v>6348554</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2113,10 +2123,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123652358</v>
+        <v>123654838</v>
       </c>
       <c r="B16" t="n">
-        <v>57507</v>
+        <v>98079</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2125,25 +2135,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2153,10 +2163,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>540555</v>
+        <v>540648</v>
       </c>
       <c r="R16" t="n">
-        <v>6348531</v>
+        <v>6348392</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2189,11 +2199,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-03-31</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2220,10 +2225,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123651343</v>
+        <v>123650824</v>
       </c>
       <c r="B17" t="n">
-        <v>100257</v>
+        <v>98079</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2232,25 +2237,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2260,10 +2265,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>540457</v>
+        <v>540485</v>
       </c>
       <c r="R17" t="n">
-        <v>6348499</v>
+        <v>6348449</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2322,7 +2327,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123650824</v>
+        <v>123653838</v>
       </c>
       <c r="B18" t="n">
         <v>98079</v>
@@ -2362,13 +2367,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>540485</v>
+        <v>540614</v>
       </c>
       <c r="R18" t="n">
-        <v>6348449</v>
+        <v>6348556</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2424,7 +2429,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123654838</v>
+        <v>123651593</v>
       </c>
       <c r="B19" t="n">
         <v>98079</v>
@@ -2464,10 +2469,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>540648</v>
+        <v>540446</v>
       </c>
       <c r="R19" t="n">
-        <v>6348392</v>
+        <v>6348497</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2526,7 +2531,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123651999</v>
+        <v>123654517</v>
       </c>
       <c r="B20" t="n">
         <v>98079</v>
@@ -2566,13 +2571,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>540507</v>
+        <v>540625</v>
       </c>
       <c r="R20" t="n">
-        <v>6348554</v>
+        <v>6348461</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2628,10 +2633,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123651753</v>
+        <v>123651201</v>
       </c>
       <c r="B21" t="n">
-        <v>57861</v>
+        <v>98079</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2640,46 +2645,41 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Tinnsjön, Tinnsjön, Sm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>540454</v>
+        <v>540472</v>
       </c>
       <c r="R21" t="n">
-        <v>6348509</v>
+        <v>6348468</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2735,10 +2735,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123654095</v>
+        <v>123655187</v>
       </c>
       <c r="B22" t="n">
-        <v>98079</v>
+        <v>92271</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2747,25 +2747,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2775,13 +2775,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>540624</v>
+        <v>540525</v>
       </c>
       <c r="R22" t="n">
-        <v>6348499</v>
+        <v>6348308</v>
       </c>
       <c r="S22" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2939,7 +2939,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123677321</v>
+        <v>123676891</v>
       </c>
       <c r="B24" t="n">
         <v>98079</v>
@@ -2979,10 +2979,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>540504</v>
+        <v>540557</v>
       </c>
       <c r="R24" t="n">
-        <v>6348434</v>
+        <v>6348447</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3041,10 +3041,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123676891</v>
+        <v>123678423</v>
       </c>
       <c r="B25" t="n">
-        <v>98079</v>
+        <v>100257</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3053,25 +3053,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3081,13 +3081,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>540557</v>
+        <v>540463</v>
       </c>
       <c r="R25" t="n">
-        <v>6348447</v>
+        <v>6348528</v>
       </c>
       <c r="S25" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3143,10 +3143,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123678423</v>
+        <v>123677388</v>
       </c>
       <c r="B26" t="n">
-        <v>100257</v>
+        <v>57644</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3155,41 +3155,46 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>222498</v>
+        <v>103021</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Tinnsjön, Tinnsjön, Sm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>540463</v>
+        <v>540515</v>
       </c>
       <c r="R26" t="n">
-        <v>6348528</v>
+        <v>6348462</v>
       </c>
       <c r="S26" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3347,10 +3352,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123677388</v>
+        <v>123677321</v>
       </c>
       <c r="B28" t="n">
-        <v>57644</v>
+        <v>98079</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3359,46 +3364,41 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Tinnsjön, Tinnsjön, Sm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>540515</v>
+        <v>540504</v>
       </c>
       <c r="R28" t="n">
-        <v>6348462</v>
+        <v>6348434</v>
       </c>
       <c r="S28" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3454,10 +3454,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123784231</v>
+        <v>123780551</v>
       </c>
       <c r="B29" t="n">
-        <v>91610</v>
+        <v>57644</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3466,41 +3466,46 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1339</v>
+        <v>103021</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Tinnsjön, Tinnsjön, Sm</t>
+          <t>Hultsfred, Hultsfred, Sm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>540612</v>
+        <v>540543</v>
       </c>
       <c r="R29" t="n">
-        <v>6348517</v>
+        <v>6348259</v>
       </c>
       <c r="S29" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3556,10 +3561,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123784690</v>
+        <v>123781316</v>
       </c>
       <c r="B30" t="n">
-        <v>96759</v>
+        <v>91260</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3568,42 +3573,38 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2606</v>
+        <v>73</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Veckticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Flavidoporia pulvinascens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Pilát) Audet</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Tinnsjön, Tinnsjön, Sm</t>
+          <t>Hultsfred, Hultsfred, Sm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>540591</v>
+        <v>540550</v>
       </c>
       <c r="R30" t="n">
-        <v>6348537</v>
+        <v>6348256</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3638,13 +3639,17 @@
           <t>2025-04-05</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>På asplåga</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3663,10 +3668,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123781316</v>
+        <v>123784690</v>
       </c>
       <c r="B31" t="n">
-        <v>91260</v>
+        <v>96759</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3675,38 +3680,42 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>73</v>
+        <v>2606</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Veckticka</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Flavidoporia pulvinascens</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Pilát) Audet</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Hultsfred, Hultsfred, Sm</t>
+          <t>Tinnsjön, Tinnsjön, Sm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>540550</v>
+        <v>540591</v>
       </c>
       <c r="R31" t="n">
-        <v>6348256</v>
+        <v>6348537</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3741,17 +3750,13 @@
           <t>2025-04-05</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>På asplåga</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3770,10 +3775,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123780551</v>
+        <v>123784231</v>
       </c>
       <c r="B32" t="n">
-        <v>57644</v>
+        <v>91610</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3782,46 +3787,41 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>103021</v>
+        <v>1339</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Hultsfred, Hultsfred, Sm</t>
+          <t>Tinnsjön, Tinnsjön, Sm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>540543</v>
+        <v>540612</v>
       </c>
       <c r="R32" t="n">
-        <v>6348259</v>
+        <v>6348517</v>
       </c>
       <c r="S32" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>

--- a/artfynd/A 14019-2025 artfynd.xlsx
+++ b/artfynd/A 14019-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123649033</v>
+        <v>123648670</v>
       </c>
       <c r="B2" t="n">
-        <v>57507</v>
+        <v>92271</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,41 +687,41 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Tinnsjön, Tinnsjön, Sm</t>
+          <t>Hultsfred, Hultsfred, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>540498</v>
+        <v>540535</v>
       </c>
       <c r="R2" t="n">
-        <v>6348264</v>
+        <v>6348224</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-03-31</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123648670</v>
+        <v>123649033</v>
       </c>
       <c r="B3" t="n">
-        <v>92271</v>
+        <v>57507</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,41 +789,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hultsfred, Hultsfred, Sm</t>
+          <t>Tinnsjön, Tinnsjön, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>540535</v>
+        <v>540498</v>
       </c>
       <c r="R3" t="n">
-        <v>6348224</v>
+        <v>6348264</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -858,6 +853,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-31</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123651287</v>
+        <v>123651343</v>
       </c>
       <c r="B4" t="n">
-        <v>98079</v>
+        <v>100257</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -896,25 +896,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,13 +924,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>540463</v>
+        <v>540457</v>
       </c>
       <c r="R4" t="n">
-        <v>6348492</v>
+        <v>6348499</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -986,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123651343</v>
+        <v>123651287</v>
       </c>
       <c r="B5" t="n">
-        <v>100257</v>
+        <v>98079</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -998,25 +998,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,13 +1026,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>540457</v>
+        <v>540463</v>
       </c>
       <c r="R5" t="n">
-        <v>6348499</v>
+        <v>6348492</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1501,10 +1501,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123652072</v>
+        <v>123651434</v>
       </c>
       <c r="B10" t="n">
-        <v>5176</v>
+        <v>98079</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1513,25 +1513,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1541,10 +1541,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>540512</v>
+        <v>540454</v>
       </c>
       <c r="R10" t="n">
-        <v>6348547</v>
+        <v>6348489</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1577,11 +1577,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-03-31</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1608,10 +1603,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123651434</v>
+        <v>123652072</v>
       </c>
       <c r="B11" t="n">
-        <v>98079</v>
+        <v>5176</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1620,25 +1615,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1648,10 +1643,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>540454</v>
+        <v>540512</v>
       </c>
       <c r="R11" t="n">
-        <v>6348489</v>
+        <v>6348547</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1684,6 +1679,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-03-31</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 14019-2025 artfynd.xlsx
+++ b/artfynd/A 14019-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123648670</v>
+        <v>123654838</v>
       </c>
       <c r="B2" t="n">
-        <v>92271</v>
+        <v>98079</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hultsfred, Hultsfred, Sm</t>
+          <t>Tinnsjön, Tinnsjön, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>540535</v>
+        <v>540648</v>
       </c>
       <c r="R2" t="n">
-        <v>6348224</v>
+        <v>6348392</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123649033</v>
+        <v>123651999</v>
       </c>
       <c r="B3" t="n">
-        <v>57507</v>
+        <v>98079</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>540498</v>
+        <v>540507</v>
       </c>
       <c r="R3" t="n">
-        <v>6348264</v>
+        <v>6348554</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -853,11 +853,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-31</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123651343</v>
+        <v>123650824</v>
       </c>
       <c r="B4" t="n">
-        <v>100257</v>
+        <v>98079</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -896,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>540457</v>
+        <v>540485</v>
       </c>
       <c r="R4" t="n">
-        <v>6348499</v>
+        <v>6348449</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -986,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123651287</v>
+        <v>123648212</v>
       </c>
       <c r="B5" t="n">
-        <v>98079</v>
+        <v>95529</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -998,41 +993,41 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>210</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Tinnsjön, Tinnsjön, Sm</t>
+          <t>Hultsfred, Hultsfred, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>540463</v>
+        <v>540478</v>
       </c>
       <c r="R5" t="n">
-        <v>6348492</v>
+        <v>6348196</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1088,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123648212</v>
+        <v>123651287</v>
       </c>
       <c r="B6" t="n">
-        <v>95529</v>
+        <v>98079</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1100,41 +1095,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>210</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hultsfred, Hultsfred, Sm</t>
+          <t>Tinnsjön, Tinnsjön, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>540478</v>
+        <v>540463</v>
       </c>
       <c r="R6" t="n">
-        <v>6348196</v>
+        <v>6348492</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1190,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123652358</v>
+        <v>123654517</v>
       </c>
       <c r="B7" t="n">
-        <v>57507</v>
+        <v>98079</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1202,25 +1197,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1230,13 +1225,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>540555</v>
+        <v>540625</v>
       </c>
       <c r="R7" t="n">
-        <v>6348531</v>
+        <v>6348461</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1266,11 +1261,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-03-31</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1297,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123651626</v>
+        <v>123649033</v>
       </c>
       <c r="B8" t="n">
-        <v>100257</v>
+        <v>57507</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1309,25 +1299,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1337,13 +1327,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>540438</v>
+        <v>540498</v>
       </c>
       <c r="R8" t="n">
-        <v>6348476</v>
+        <v>6348264</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1373,6 +1363,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-03-31</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1399,10 +1394,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123648565</v>
+        <v>123653838</v>
       </c>
       <c r="B9" t="n">
-        <v>91010</v>
+        <v>98079</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1411,41 +1406,41 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Hultsfred, Hultsfred, Sm</t>
+          <t>Tinnsjön, Tinnsjön, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>540519</v>
+        <v>540614</v>
       </c>
       <c r="R9" t="n">
-        <v>6348230</v>
+        <v>6348556</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1501,7 +1496,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123651434</v>
+        <v>123651201</v>
       </c>
       <c r="B10" t="n">
         <v>98079</v>
@@ -1541,13 +1536,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>540454</v>
+        <v>540472</v>
       </c>
       <c r="R10" t="n">
-        <v>6348489</v>
+        <v>6348468</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1603,10 +1598,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123652072</v>
+        <v>123652358</v>
       </c>
       <c r="B11" t="n">
-        <v>5176</v>
+        <v>57507</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1615,25 +1610,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1643,13 +1638,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>540512</v>
+        <v>540555</v>
       </c>
       <c r="R11" t="n">
-        <v>6348547</v>
+        <v>6348531</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1683,7 +1678,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Gnaggångar och kläckhål</t>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1710,10 +1705,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123653223</v>
+        <v>123655187</v>
       </c>
       <c r="B12" t="n">
-        <v>96368</v>
+        <v>92271</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1726,21 +1721,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2590</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1750,13 +1745,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>540587</v>
+        <v>540525</v>
       </c>
       <c r="R12" t="n">
-        <v>6348578</v>
+        <v>6348308</v>
       </c>
       <c r="S12" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1812,10 +1807,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123651753</v>
+        <v>123651593</v>
       </c>
       <c r="B13" t="n">
-        <v>57861</v>
+        <v>98079</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1824,46 +1819,41 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Tinnsjön, Tinnsjön, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>540454</v>
+        <v>540446</v>
       </c>
       <c r="R13" t="n">
-        <v>6348509</v>
+        <v>6348497</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1919,10 +1909,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123654095</v>
+        <v>123653223</v>
       </c>
       <c r="B14" t="n">
-        <v>98079</v>
+        <v>96368</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1931,25 +1921,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>2590</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1959,10 +1949,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>540624</v>
+        <v>540587</v>
       </c>
       <c r="R14" t="n">
-        <v>6348499</v>
+        <v>6348578</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2021,7 +2011,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123651999</v>
+        <v>123651434</v>
       </c>
       <c r="B15" t="n">
         <v>98079</v>
@@ -2061,10 +2051,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>540507</v>
+        <v>540454</v>
       </c>
       <c r="R15" t="n">
-        <v>6348554</v>
+        <v>6348489</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2123,10 +2113,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123654838</v>
+        <v>123648565</v>
       </c>
       <c r="B16" t="n">
-        <v>98079</v>
+        <v>91010</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2135,41 +2125,41 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Tinnsjön, Tinnsjön, Sm</t>
+          <t>Hultsfred, Hultsfred, Sm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>540648</v>
+        <v>540519</v>
       </c>
       <c r="R16" t="n">
-        <v>6348392</v>
+        <v>6348230</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2225,10 +2215,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123650824</v>
+        <v>123652072</v>
       </c>
       <c r="B17" t="n">
-        <v>98079</v>
+        <v>5176</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2237,25 +2227,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2265,13 +2255,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>540485</v>
+        <v>540512</v>
       </c>
       <c r="R17" t="n">
-        <v>6348449</v>
+        <v>6348547</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2301,6 +2291,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-03-31</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2327,10 +2322,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123653838</v>
+        <v>123651343</v>
       </c>
       <c r="B18" t="n">
-        <v>98079</v>
+        <v>100257</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2339,25 +2334,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2367,13 +2362,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>540614</v>
+        <v>540457</v>
       </c>
       <c r="R18" t="n">
-        <v>6348556</v>
+        <v>6348499</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2429,10 +2424,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123651593</v>
+        <v>123648670</v>
       </c>
       <c r="B19" t="n">
-        <v>98079</v>
+        <v>92271</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2441,38 +2436,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Tinnsjön, Tinnsjön, Sm</t>
+          <t>Hultsfred, Hultsfred, Sm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>540446</v>
+        <v>540535</v>
       </c>
       <c r="R19" t="n">
-        <v>6348497</v>
+        <v>6348224</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2531,7 +2526,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123654517</v>
+        <v>123654095</v>
       </c>
       <c r="B20" t="n">
         <v>98079</v>
@@ -2571,10 +2566,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>540625</v>
+        <v>540624</v>
       </c>
       <c r="R20" t="n">
-        <v>6348461</v>
+        <v>6348499</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2633,10 +2628,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123651201</v>
+        <v>123651753</v>
       </c>
       <c r="B21" t="n">
-        <v>98079</v>
+        <v>57861</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2645,41 +2640,46 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Tinnsjön, Tinnsjön, Sm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>540472</v>
+        <v>540454</v>
       </c>
       <c r="R21" t="n">
-        <v>6348468</v>
+        <v>6348509</v>
       </c>
       <c r="S21" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2735,10 +2735,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123655187</v>
+        <v>123651626</v>
       </c>
       <c r="B22" t="n">
-        <v>92271</v>
+        <v>100257</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2751,21 +2751,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4364</v>
+        <v>222498</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2775,10 +2775,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>540525</v>
+        <v>540438</v>
       </c>
       <c r="R22" t="n">
-        <v>6348308</v>
+        <v>6348476</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2939,10 +2939,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123676891</v>
+        <v>123678423</v>
       </c>
       <c r="B24" t="n">
-        <v>98079</v>
+        <v>100257</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2951,25 +2951,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2979,13 +2979,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>540557</v>
+        <v>540463</v>
       </c>
       <c r="R24" t="n">
-        <v>6348447</v>
+        <v>6348528</v>
       </c>
       <c r="S24" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3041,10 +3041,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123678423</v>
+        <v>123676068</v>
       </c>
       <c r="B25" t="n">
-        <v>100257</v>
+        <v>96957</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3057,37 +3057,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Tinnsjön, Tinnsjön, Sm</t>
+          <t>Hultsfred, Hultsfred, Sm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>540463</v>
+        <v>540573</v>
       </c>
       <c r="R25" t="n">
-        <v>6348528</v>
+        <v>6348225</v>
       </c>
       <c r="S25" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3143,10 +3143,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123677388</v>
+        <v>123676891</v>
       </c>
       <c r="B26" t="n">
-        <v>57644</v>
+        <v>98079</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3155,46 +3155,41 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Tinnsjön, Tinnsjön, Sm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>540515</v>
+        <v>540557</v>
       </c>
       <c r="R26" t="n">
-        <v>6348462</v>
+        <v>6348447</v>
       </c>
       <c r="S26" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3250,10 +3245,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123676068</v>
+        <v>123677321</v>
       </c>
       <c r="B27" t="n">
-        <v>96957</v>
+        <v>98079</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3262,41 +3257,41 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Hultsfred, Hultsfred, Sm</t>
+          <t>Tinnsjön, Tinnsjön, Sm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>540573</v>
+        <v>540504</v>
       </c>
       <c r="R27" t="n">
-        <v>6348225</v>
+        <v>6348434</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3352,10 +3347,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123677321</v>
+        <v>123677388</v>
       </c>
       <c r="B28" t="n">
-        <v>98079</v>
+        <v>57644</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3364,41 +3359,46 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Tinnsjön, Tinnsjön, Sm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>540504</v>
+        <v>540515</v>
       </c>
       <c r="R28" t="n">
-        <v>6348434</v>
+        <v>6348462</v>
       </c>
       <c r="S28" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3454,10 +3454,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123780551</v>
+        <v>123784690</v>
       </c>
       <c r="B29" t="n">
-        <v>57644</v>
+        <v>96759</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3466,46 +3466,45 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103021</v>
+        <v>2606</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Hultsfred, Hultsfred, Sm</t>
+          <t>Tinnsjön, Tinnsjön, Sm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>540543</v>
+        <v>540591</v>
       </c>
       <c r="R29" t="n">
-        <v>6348259</v>
+        <v>6348537</v>
       </c>
       <c r="S29" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3543,6 +3542,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3668,10 +3668,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123784690</v>
+        <v>123780551</v>
       </c>
       <c r="B31" t="n">
-        <v>96759</v>
+        <v>57644</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3680,45 +3680,46 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2606</v>
+        <v>103021</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Tinnsjön, Tinnsjön, Sm</t>
+          <t>Hultsfred, Hultsfred, Sm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>540591</v>
+        <v>540543</v>
       </c>
       <c r="R31" t="n">
-        <v>6348537</v>
+        <v>6348259</v>
       </c>
       <c r="S31" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3756,7 +3757,6 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 14019-2025 artfynd.xlsx
+++ b/artfynd/A 14019-2025 artfynd.xlsx
@@ -3556,10 +3556,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123781316</v>
+        <v>123784690</v>
       </c>
       <c r="B30" t="n">
-        <v>91282</v>
+        <v>96781</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3568,38 +3568,42 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>73</v>
+        <v>2606</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Veckticka</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Flavidoporia pulvinascens</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Pilát) Audet</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Hultsfred, Hultsfred, Sm</t>
+          <t>Tinnsjön, Tinnsjön, Sm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>540550</v>
+        <v>540591</v>
       </c>
       <c r="R30" t="n">
-        <v>6348256</v>
+        <v>6348537</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3634,17 +3638,13 @@
           <t>2025-04-05</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>På asplåga</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3663,10 +3663,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123784690</v>
+        <v>123780551</v>
       </c>
       <c r="B31" t="n">
-        <v>96781</v>
+        <v>57666</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3675,45 +3675,46 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2606</v>
+        <v>103021</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Tinnsjön, Tinnsjön, Sm</t>
+          <t>Hultsfred, Hultsfred, Sm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>540591</v>
+        <v>540543</v>
       </c>
       <c r="R31" t="n">
-        <v>6348537</v>
+        <v>6348259</v>
       </c>
       <c r="S31" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3751,7 +3752,6 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3770,10 +3770,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123780551</v>
+        <v>123781316</v>
       </c>
       <c r="B32" t="n">
-        <v>57666</v>
+        <v>91282</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3786,42 +3786,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>103021</v>
+        <v>73</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Veckticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Flavidoporia pulvinascens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Pilát) Audet</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Hultsfred, Hultsfred, Sm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>540543</v>
+        <v>540550</v>
       </c>
       <c r="R32" t="n">
-        <v>6348259</v>
+        <v>6348256</v>
       </c>
       <c r="S32" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3851,6 +3846,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-04-05</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>På asplåga</t>
         </is>
       </c>
       <c r="AD32" t="b">
